--- a/output/ranking_pib_per_capita_ppc_2021.xlsx
+++ b/output/ranking_pib_per_capita_ppc_2021.xlsx
@@ -12,8 +12,9 @@
     <sheet name="1995-2002" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2003-2016" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2003-2018" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2019-2022" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2023-2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2003-2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2019-2022" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2023-2025" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1995-2002'!$A$6:$K$194</definedName>
@@ -22,10 +23,12 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2003-2016'!$1:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2003-2018'!$A$6:$K$199</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2003-2018'!$1:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2019-2022'!$A$6:$K$205</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2019-2022'!$1:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2023-2025'!$A$6:$K$191</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2023-2025'!$1:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2003-2025'!$A$6:$K$188</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2003-2025'!$1:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2019-2022'!$A$6:$K$205</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2019-2022'!$1:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2023-2025'!$A$6:$K$191</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'2023-2025'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -901,7 +904,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>1995–2002 (7 anos); 2003–2016 (13 anos); 2003–2018 (15 anos); 2019–2022 (3 anos); 2023–2025 (2 anos).</t>
+          <t>1995–2002 (7 anos); 2003–2016 (13 anos); 2003–2018 (15 anos); 2003–2025 (22 anos); 2019–2022 (3 anos); 2023–2025 (2 anos).</t>
         </is>
       </c>
     </row>
@@ -913,7 +916,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>1995–2002: 188 países; 2003–2016: 193 países; 2003–2018: 193 países; 2019–2022: 199 países; 2023–2025: 185 países</t>
+          <t>1995–2002: 188 países; 2003–2016: 193 países; 2003–2018: 193 países; 2003–2025: 182 países; 2019–2022: 199 países; 2023–2025: 185 países</t>
         </is>
       </c>
     </row>
@@ -955,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1193,80 +1196,120 @@
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>2019–2022</t>
+          <t>2003–2025</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>0.04453196799004644</v>
+        <v>0.6340441922652669</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.01462893988803859</v>
+        <v>0.02257179340520721</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.02971510806659805</v>
+        <v>0.4043188351725531</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.009808514516075784</v>
+        <v>0.01555392104535014</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0.1423295335043913</v>
+        <v>3.828115948209115</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.0453550020578577</v>
+        <v>0.0741892557085031</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>55</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>2019–2022</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>199</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0.04453196799004644</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0.01462893988803859</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.02971510806659805</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.009808514516075784</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.1423295335043913</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.0453550020578577</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
           <t>2023–2025</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B10" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C10" s="16" t="n">
         <v>185</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.04875087978157322</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E10" s="17" t="n">
         <v>0.02408538695832063</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.04952274171879711</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.02446217193159317</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I10" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J10" s="15" t="n">
         <v>0.1048725328699756</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="K10" s="15" t="n">
         <v>0.05112917040198983</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L10" s="16" t="n">
         <v>113</v>
       </c>
     </row>
@@ -2028,7 +2071,7 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>Top 10 — 2019–2022</t>
+          <t>Top 10 — 2003–2025</t>
         </is>
       </c>
       <c r="B56" s="19" t="n"/>
@@ -2276,7 +2319,7 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>Top 10 — 2023–2025</t>
+          <t>Top 10 — 2019–2022</t>
         </is>
       </c>
       <c r="B70" s="19" t="n"/>
@@ -2521,13 +2564,262 @@
         <v>0.06335281979428364</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>Top 10 — 2023–2025</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="n"/>
+      <c r="C84" s="19" t="n"/>
+      <c r="D84" s="19" t="n"/>
+      <c r="E84" s="19" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>ISO3</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>Variação %</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>CAGR % a.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="n">
+        <v>0.6965052331788913</v>
+      </c>
+      <c r="E86" s="23" t="n">
+        <v>0.3024996096655428</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Kyrgyz Republic</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>KGZ</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="n">
+        <v>0.1981019183281576</v>
+      </c>
+      <c r="E87" s="23" t="n">
+        <v>0.09457842036473461</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>Palau</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="n">
+        <v>0.1947844362232367</v>
+      </c>
+      <c r="E88" s="23" t="n">
+        <v>0.09306195443041411</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>XKX</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="n">
+        <v>0.1559732909766427</v>
+      </c>
+      <c r="E89" s="23" t="n">
+        <v>0.07516198359904935</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Bhutan</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>BTN</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="n">
+        <v>0.1460322562149521</v>
+      </c>
+      <c r="E90" s="23" t="n">
+        <v>0.07052896094171701</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="n">
+        <v>0.1420449645869883</v>
+      </c>
+      <c r="E91" s="23" t="n">
+        <v>0.06866503853498851</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>TJK</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="n">
+        <v>0.1318157741219854</v>
+      </c>
+      <c r="E92" s="23" t="n">
+        <v>0.06386830675699029</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D93" s="25" t="n">
+        <v>0.1317303412522746</v>
+      </c>
+      <c r="E93" s="25" t="n">
+        <v>0.06382815400433661</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>LBY</t>
+        </is>
+      </c>
+      <c r="D94" s="23" t="n">
+        <v>0.1315750506645685</v>
+      </c>
+      <c r="E94" s="23" t="n">
+        <v>0.06375516481217081</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>Marshall Islands</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="inlineStr">
+        <is>
+          <t>MHL</t>
+        </is>
+      </c>
+      <c r="D95" s="23" t="n">
+        <v>0.1307192193644542</v>
+      </c>
+      <c r="E95" s="23" t="n">
+        <v>0.06335281979428364</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A56:E56"/>
@@ -28882,6 +29174,8366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:K188"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Ranking da variação do PIB per capita em PPC — 2003 a 2025</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>PIB per capita, PPC (dólares internacionais constantes de 2021)  |  22 anos  |  182 países  |  Fonte: Banco Mundial (NY.GDP.PCAP.PP.KD)</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Mundo (referência, fora do ranking): 13,410.6 → 21,913.5  |  variação +63.40%  |  CAGR +2.26% a.a.  |  equivaleria à 72ª posição entre 182 países</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="n"/>
+      <c r="C3" s="29" t="n"/>
+      <c r="D3" s="29" t="n"/>
+      <c r="E3" s="29" t="n"/>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="29" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="29" t="n"/>
+      <c r="J3" s="29" t="n"/>
+      <c r="K3" s="29" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Brasil destacado em amarelo; China em laranja. Valores em dólares internacionais constantes de 2021.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>ISO3</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Região</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Faixa de renda</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PIB pc 2003</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>PIB pc 2025</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Variação absoluta</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Variação %</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>CAGR % a.a.</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Vs. mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>8267.42910545363</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>83658.6773475997</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>75391.24824214607</v>
+      </c>
+      <c r="I7" s="34" t="n">
+        <v>9.119068005362641</v>
+      </c>
+      <c r="J7" s="34" t="n">
+        <v>0.1109338636750807</v>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>5191.78118308167</v>
+      </c>
+      <c r="G8" s="37" t="n">
+        <v>25066.5215296486</v>
+      </c>
+      <c r="H8" s="37" t="n">
+        <v>19874.74034656693</v>
+      </c>
+      <c r="I8" s="38" t="n">
+        <v>3.828115948209115</v>
+      </c>
+      <c r="J8" s="38" t="n">
+        <v>0.0741892557085031</v>
+      </c>
+      <c r="K8" s="35" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Ethiopia</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>795.772138298998</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>3094.86811868352</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>2299.095980384522</v>
+      </c>
+      <c r="I9" s="34" t="n">
+        <v>2.889138573384779</v>
+      </c>
+      <c r="J9" s="34" t="n">
+        <v>0.06368128719719568</v>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>Turkmenistan</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>TKM</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>5154.7509814614</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>19313.9430262025</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>14159.1920447411</v>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>2.746823676965845</v>
+      </c>
+      <c r="J10" s="34" t="n">
+        <v>0.06188039461930583</v>
+      </c>
+      <c r="K10" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>GEO</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>7227.73705960701</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>25135.7822457412</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>17908.04518613419</v>
+      </c>
+      <c r="I11" s="34" t="n">
+        <v>2.477683545824493</v>
+      </c>
+      <c r="J11" s="34" t="n">
+        <v>0.05828854097277492</v>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>6569.26023440631</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <v>21153.478328571</v>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>14584.21809416469</v>
+      </c>
+      <c r="I12" s="34" t="n">
+        <v>2.220070080003875</v>
+      </c>
+      <c r="J12" s="34" t="n">
+        <v>0.05459276473935892</v>
+      </c>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>2309.83931482788</v>
+      </c>
+      <c r="G13" s="33" t="n">
+        <v>7300.08078250634</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <v>4990.24146767846</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>2.160427972475788</v>
+      </c>
+      <c r="J13" s="34" t="n">
+        <v>0.05369694911389877</v>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="n">
+        <v>3733.79819347394</v>
+      </c>
+      <c r="G14" s="33" t="n">
+        <v>11622.8556243531</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <v>7889.05743087916</v>
+      </c>
+      <c r="I14" s="34" t="n">
+        <v>2.112877296011317</v>
+      </c>
+      <c r="J14" s="34" t="n">
+        <v>0.05297110725890852</v>
+      </c>
+      <c r="K14" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>AZE</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>7329.40601818943</v>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>22314.2168957333</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>14984.81087754387</v>
+      </c>
+      <c r="I15" s="34" t="n">
+        <v>2.044478207423082</v>
+      </c>
+      <c r="J15" s="34" t="n">
+        <v>0.05190824144108586</v>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Viet Nam</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="n">
+        <v>5090.28990869885</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>15457.3499403547</v>
+      </c>
+      <c r="H16" s="33" t="n">
+        <v>10367.06003165585</v>
+      </c>
+      <c r="I16" s="34" t="n">
+        <v>2.036634497760033</v>
+      </c>
+      <c r="J16" s="34" t="n">
+        <v>0.05178490301321226</v>
+      </c>
+      <c r="K16" s="31" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="n">
+        <v>3346.8882902915</v>
+      </c>
+      <c r="G17" s="49" t="n">
+        <v>10039.0708910587</v>
+      </c>
+      <c r="H17" s="49" t="n">
+        <v>6692.1826007672</v>
+      </c>
+      <c r="I17" s="50" t="n">
+        <v>1.99952374274922</v>
+      </c>
+      <c r="J17" s="50" t="n">
+        <v>0.0511972005237693</v>
+      </c>
+      <c r="K17" s="47" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F18" s="45" t="n">
+        <v>2958.91503115633</v>
+      </c>
+      <c r="G18" s="45" t="n">
+        <v>8676.755762250799</v>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>5717.840731094469</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>1.93241126253631</v>
+      </c>
+      <c r="J18" s="46" t="n">
+        <v>0.05011652923043464</v>
+      </c>
+      <c r="K18" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>TJK</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="n">
+        <v>1736.64039749855</v>
+      </c>
+      <c r="G19" s="41" t="n">
+        <v>5061.84700623649</v>
+      </c>
+      <c r="H19" s="41" t="n">
+        <v>3325.20660873794</v>
+      </c>
+      <c r="I19" s="42" t="n">
+        <v>1.914735263286259</v>
+      </c>
+      <c r="J19" s="42" t="n">
+        <v>0.04982797565860064</v>
+      </c>
+      <c r="K19" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>8025.2480324802</v>
+      </c>
+      <c r="G20" s="45" t="n">
+        <v>22724.2938194949</v>
+      </c>
+      <c r="H20" s="45" t="n">
+        <v>14699.0457870147</v>
+      </c>
+      <c r="I20" s="46" t="n">
+        <v>1.831600185754255</v>
+      </c>
+      <c r="J20" s="46" t="n">
+        <v>0.04844802517026103</v>
+      </c>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F21" s="41" t="n">
+        <v>1266.94449487196</v>
+      </c>
+      <c r="G21" s="41" t="n">
+        <v>3558.68003753808</v>
+      </c>
+      <c r="H21" s="41" t="n">
+        <v>2291.73554266612</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>1.808868148480117</v>
+      </c>
+      <c r="J21" s="42" t="n">
+        <v>0.0480639641687699</v>
+      </c>
+      <c r="K21" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>MNG</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>6463.78966651762</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>17772.5342212559</v>
+      </c>
+      <c r="H22" s="45" t="n">
+        <v>11308.74455473828</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>1.749553302038507</v>
+      </c>
+      <c r="J22" s="46" t="n">
+        <v>0.04704768533583592</v>
+      </c>
+      <c r="K22" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="D23" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F23" s="41" t="n">
+        <v>1874.17128269389</v>
+      </c>
+      <c r="G23" s="41" t="n">
+        <v>5137.10048825615</v>
+      </c>
+      <c r="H23" s="41" t="n">
+        <v>3262.92920556226</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>1.740998400568918</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>0.04689938491072576</v>
+      </c>
+      <c r="K23" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>Lao PDR</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="D24" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F24" s="45" t="n">
+        <v>3282.9853971272</v>
+      </c>
+      <c r="G24" s="45" t="n">
+        <v>8872.69396186433</v>
+      </c>
+      <c r="H24" s="45" t="n">
+        <v>5589.70856473713</v>
+      </c>
+      <c r="I24" s="46" t="n">
+        <v>1.70262973744216</v>
+      </c>
+      <c r="J24" s="46" t="n">
+        <v>0.04622877721276608</v>
+      </c>
+      <c r="K24" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>Bhutan</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>BTN</t>
+        </is>
+      </c>
+      <c r="D25" s="40" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E25" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F25" s="41" t="n">
+        <v>6323.5411950973</v>
+      </c>
+      <c r="G25" s="41" t="n">
+        <v>16743.8703854575</v>
+      </c>
+      <c r="H25" s="41" t="n">
+        <v>10420.3291903602</v>
+      </c>
+      <c r="I25" s="42" t="n">
+        <v>1.647862940853327</v>
+      </c>
+      <c r="J25" s="42" t="n">
+        <v>0.04525564767389634</v>
+      </c>
+      <c r="K25" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F26" s="45" t="n">
+        <v>14957.5590503323</v>
+      </c>
+      <c r="G26" s="45" t="n">
+        <v>37516.1796428548</v>
+      </c>
+      <c r="H26" s="45" t="n">
+        <v>22558.6205925225</v>
+      </c>
+      <c r="I26" s="46" t="n">
+        <v>1.508175265537149</v>
+      </c>
+      <c r="J26" s="46" t="n">
+        <v>0.04268381178276881</v>
+      </c>
+      <c r="K26" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>Turkiye</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E27" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F27" s="41" t="n">
+        <v>15255.7177960689</v>
+      </c>
+      <c r="G27" s="41" t="n">
+        <v>37300.7485739354</v>
+      </c>
+      <c r="H27" s="41" t="n">
+        <v>22045.0307778665</v>
+      </c>
+      <c r="I27" s="42" t="n">
+        <v>1.445033991356806</v>
+      </c>
+      <c r="J27" s="42" t="n">
+        <v>0.04147611334881196</v>
+      </c>
+      <c r="K27" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>BIH</t>
+        </is>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F28" s="45" t="n">
+        <v>8709.956715781969</v>
+      </c>
+      <c r="G28" s="45" t="n">
+        <v>21178.2260059497</v>
+      </c>
+      <c r="H28" s="45" t="n">
+        <v>12468.26929016773</v>
+      </c>
+      <c r="I28" s="46" t="n">
+        <v>1.431496125299441</v>
+      </c>
+      <c r="J28" s="46" t="n">
+        <v>0.04121330313178673</v>
+      </c>
+      <c r="K28" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F29" s="41" t="n">
+        <v>7034.35784911687</v>
+      </c>
+      <c r="G29" s="41" t="n">
+        <v>17087.1874044819</v>
+      </c>
+      <c r="H29" s="41" t="n">
+        <v>10052.82955536503</v>
+      </c>
+      <c r="I29" s="42" t="n">
+        <v>1.429104087536166</v>
+      </c>
+      <c r="J29" s="42" t="n">
+        <v>0.04116672141685251</v>
+      </c>
+      <c r="K29" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F30" s="45" t="n">
+        <v>20310.7119582322</v>
+      </c>
+      <c r="G30" s="45" t="n">
+        <v>48839.5436452948</v>
+      </c>
+      <c r="H30" s="45" t="n">
+        <v>28528.8316870626</v>
+      </c>
+      <c r="I30" s="46" t="n">
+        <v>1.404619973230406</v>
+      </c>
+      <c r="J30" s="46" t="n">
+        <v>0.0406873922430977</v>
+      </c>
+      <c r="K30" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F31" s="41" t="n">
+        <v>19855.6317989181</v>
+      </c>
+      <c r="G31" s="41" t="n">
+        <v>46924.5887897477</v>
+      </c>
+      <c r="H31" s="41" t="n">
+        <v>27068.9569908296</v>
+      </c>
+      <c r="I31" s="42" t="n">
+        <v>1.363288625865058</v>
+      </c>
+      <c r="J31" s="42" t="n">
+        <v>0.03986757129620666</v>
+      </c>
+      <c r="K31" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F32" s="45" t="n">
+        <v>17587.462617764</v>
+      </c>
+      <c r="G32" s="45" t="n">
+        <v>40845.9843440113</v>
+      </c>
+      <c r="H32" s="45" t="n">
+        <v>23258.52172624731</v>
+      </c>
+      <c r="I32" s="46" t="n">
+        <v>1.322448964454675</v>
+      </c>
+      <c r="J32" s="46" t="n">
+        <v>0.0390439482911269</v>
+      </c>
+      <c r="K32" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F33" s="41" t="n">
+        <v>15271.4839489061</v>
+      </c>
+      <c r="G33" s="41" t="n">
+        <v>35325.5317883474</v>
+      </c>
+      <c r="H33" s="41" t="n">
+        <v>20054.0478394413</v>
+      </c>
+      <c r="I33" s="42" t="n">
+        <v>1.313169558802291</v>
+      </c>
+      <c r="J33" s="42" t="n">
+        <v>0.03885488171150953</v>
+      </c>
+      <c r="K33" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F34" s="45" t="n">
+        <v>6599.09193597034</v>
+      </c>
+      <c r="G34" s="45" t="n">
+        <v>15091.0088604652</v>
+      </c>
+      <c r="H34" s="45" t="n">
+        <v>8491.916924494859</v>
+      </c>
+      <c r="I34" s="46" t="n">
+        <v>1.286831128720469</v>
+      </c>
+      <c r="J34" s="46" t="n">
+        <v>0.03831426942967431</v>
+      </c>
+      <c r="K34" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="n">
+        <v>29</v>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F35" s="41" t="n">
+        <v>58608.3353816693</v>
+      </c>
+      <c r="G35" s="41" t="n">
+        <v>131338.444745041</v>
+      </c>
+      <c r="H35" s="41" t="n">
+        <v>72730.1093633717</v>
+      </c>
+      <c r="I35" s="42" t="n">
+        <v>1.240951630680833</v>
+      </c>
+      <c r="J35" s="42" t="n">
+        <v>0.03735821183284305</v>
+      </c>
+      <c r="K35" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F36" s="45" t="n">
+        <v>11000.8684059352</v>
+      </c>
+      <c r="G36" s="45" t="n">
+        <v>24543.3421843415</v>
+      </c>
+      <c r="H36" s="45" t="n">
+        <v>13542.4737784063</v>
+      </c>
+      <c r="I36" s="46" t="n">
+        <v>1.231036794431597</v>
+      </c>
+      <c r="J36" s="46" t="n">
+        <v>0.03714914849281947</v>
+      </c>
+      <c r="K36" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="C37" s="39" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E37" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="n">
+        <v>13413.9265504854</v>
+      </c>
+      <c r="G37" s="41" t="n">
+        <v>29666.2115719117</v>
+      </c>
+      <c r="H37" s="41" t="n">
+        <v>16252.2850214263</v>
+      </c>
+      <c r="I37" s="42" t="n">
+        <v>1.211597883755983</v>
+      </c>
+      <c r="J37" s="42" t="n">
+        <v>0.03673667480488141</v>
+      </c>
+      <c r="K37" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F38" s="45" t="n">
+        <v>17344.752672995</v>
+      </c>
+      <c r="G38" s="45" t="n">
+        <v>37850.5791042984</v>
+      </c>
+      <c r="H38" s="45" t="n">
+        <v>20505.8264313034</v>
+      </c>
+      <c r="I38" s="46" t="n">
+        <v>1.182249572415642</v>
+      </c>
+      <c r="J38" s="46" t="n">
+        <v>0.03610733018068712</v>
+      </c>
+      <c r="K38" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="inlineStr">
+        <is>
+          <t>LKA</t>
+        </is>
+      </c>
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F39" s="41" t="n">
+        <v>6741.01248848024</v>
+      </c>
+      <c r="G39" s="41" t="n">
+        <v>14582.7603740374</v>
+      </c>
+      <c r="H39" s="41" t="n">
+        <v>7841.74788555716</v>
+      </c>
+      <c r="I39" s="42" t="n">
+        <v>1.163289327672656</v>
+      </c>
+      <c r="J39" s="42" t="n">
+        <v>0.03569643695153735</v>
+      </c>
+      <c r="K39" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>NPL</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F40" s="45" t="n">
+        <v>2439.49479601556</v>
+      </c>
+      <c r="G40" s="45" t="n">
+        <v>5276.92387725538</v>
+      </c>
+      <c r="H40" s="45" t="n">
+        <v>2837.42908123982</v>
+      </c>
+      <c r="I40" s="46" t="n">
+        <v>1.163121596272395</v>
+      </c>
+      <c r="J40" s="46" t="n">
+        <v>0.03569278667608389</v>
+      </c>
+      <c r="K40" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="D41" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F41" s="41" t="n">
+        <v>5003.38317718716</v>
+      </c>
+      <c r="G41" s="41" t="n">
+        <v>10747.5454408601</v>
+      </c>
+      <c r="H41" s="41" t="n">
+        <v>5744.16226367294</v>
+      </c>
+      <c r="I41" s="42" t="n">
+        <v>1.14805563760604</v>
+      </c>
+      <c r="J41" s="42" t="n">
+        <v>0.03536380482191825</v>
+      </c>
+      <c r="K41" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F42" s="45" t="n">
+        <v>4841.265398715</v>
+      </c>
+      <c r="G42" s="45" t="n">
+        <v>10395.7415044012</v>
+      </c>
+      <c r="H42" s="45" t="n">
+        <v>5554.4761056862</v>
+      </c>
+      <c r="I42" s="46" t="n">
+        <v>1.147319068101597</v>
+      </c>
+      <c r="J42" s="46" t="n">
+        <v>0.03534766459667282</v>
+      </c>
+      <c r="K42" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E43" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F43" s="41" t="n">
+        <v>3507.75105744843</v>
+      </c>
+      <c r="G43" s="41" t="n">
+        <v>7357.83332993014</v>
+      </c>
+      <c r="H43" s="41" t="n">
+        <v>3850.08227248171</v>
+      </c>
+      <c r="I43" s="42" t="n">
+        <v>1.097592790772985</v>
+      </c>
+      <c r="J43" s="42" t="n">
+        <v>0.03424561935980774</v>
+      </c>
+      <c r="K43" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>SRB</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F44" s="45" t="n">
+        <v>13273.6900656327</v>
+      </c>
+      <c r="G44" s="45" t="n">
+        <v>27603.3916309287</v>
+      </c>
+      <c r="H44" s="45" t="n">
+        <v>14329.701565296</v>
+      </c>
+      <c r="I44" s="46" t="n">
+        <v>1.07955673926706</v>
+      </c>
+      <c r="J44" s="46" t="n">
+        <v>0.0338397278987852</v>
+      </c>
+      <c r="K44" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="n">
+        <v>39</v>
+      </c>
+      <c r="B45" s="40" t="inlineStr">
+        <is>
+          <t>North Macedonia</t>
+        </is>
+      </c>
+      <c r="C45" s="39" t="inlineStr">
+        <is>
+          <t>MKD</t>
+        </is>
+      </c>
+      <c r="D45" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E45" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F45" s="41" t="n">
+        <v>12077.849005462</v>
+      </c>
+      <c r="G45" s="41" t="n">
+        <v>25094.6225007185</v>
+      </c>
+      <c r="H45" s="41" t="n">
+        <v>13016.7734952565</v>
+      </c>
+      <c r="I45" s="42" t="n">
+        <v>1.077739379699969</v>
+      </c>
+      <c r="J45" s="42" t="n">
+        <v>0.03379864303687197</v>
+      </c>
+      <c r="K45" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F46" s="45" t="n">
+        <v>18717.6675525538</v>
+      </c>
+      <c r="G46" s="45" t="n">
+        <v>38800.5425281872</v>
+      </c>
+      <c r="H46" s="45" t="n">
+        <v>20082.8749756334</v>
+      </c>
+      <c r="I46" s="46" t="n">
+        <v>1.072936834637462</v>
+      </c>
+      <c r="J46" s="46" t="n">
+        <v>0.03368990707065178</v>
+      </c>
+      <c r="K46" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" s="40" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C47" s="39" t="inlineStr">
+        <is>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F47" s="41" t="n">
+        <v>32147.8757483202</v>
+      </c>
+      <c r="G47" s="41" t="n">
+        <v>63655.5160659665</v>
+      </c>
+      <c r="H47" s="41" t="n">
+        <v>31507.6403176463</v>
+      </c>
+      <c r="I47" s="42" t="n">
+        <v>0.9800846738463784</v>
+      </c>
+      <c r="J47" s="42" t="n">
+        <v>0.03153893661153861</v>
+      </c>
+      <c r="K47" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>Kyrgyz Republic</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
+        <is>
+          <t>KGZ</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F48" s="45" t="n">
+        <v>3982.92722017802</v>
+      </c>
+      <c r="G48" s="45" t="n">
+        <v>7878.4491366966</v>
+      </c>
+      <c r="H48" s="45" t="n">
+        <v>3895.52191651858</v>
+      </c>
+      <c r="I48" s="46" t="n">
+        <v>0.9780550085834778</v>
+      </c>
+      <c r="J48" s="46" t="n">
+        <v>0.03149085088763992</v>
+      </c>
+      <c r="K48" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="C49" s="39" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E49" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F49" s="41" t="n">
+        <v>14551.8784442579</v>
+      </c>
+      <c r="G49" s="41" t="n">
+        <v>28769.5128307709</v>
+      </c>
+      <c r="H49" s="41" t="n">
+        <v>14217.634386513</v>
+      </c>
+      <c r="I49" s="42" t="n">
+        <v>0.977030865188625</v>
+      </c>
+      <c r="J49" s="42" t="n">
+        <v>0.03146656955916871</v>
+      </c>
+      <c r="K49" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F50" s="45" t="n">
+        <v>8173.27672987692</v>
+      </c>
+      <c r="G50" s="45" t="n">
+        <v>16079.1247394843</v>
+      </c>
+      <c r="H50" s="45" t="n">
+        <v>7905.848009607379</v>
+      </c>
+      <c r="I50" s="46" t="n">
+        <v>0.9672801094214794</v>
+      </c>
+      <c r="J50" s="46" t="n">
+        <v>0.03123478650204103</v>
+      </c>
+      <c r="K50" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="40" t="inlineStr">
+        <is>
+          <t>Slovak Republic</t>
+        </is>
+      </c>
+      <c r="C51" s="39" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="D51" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E51" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F51" s="41" t="n">
+        <v>20721.7128107535</v>
+      </c>
+      <c r="G51" s="41" t="n">
+        <v>40689.8179557427</v>
+      </c>
+      <c r="H51" s="41" t="n">
+        <v>19968.1051449892</v>
+      </c>
+      <c r="I51" s="42" t="n">
+        <v>0.9636319800082735</v>
+      </c>
+      <c r="J51" s="42" t="n">
+        <v>0.0311477856354927</v>
+      </c>
+      <c r="K51" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="D52" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F52" s="45" t="n">
+        <v>16694.4326030244</v>
+      </c>
+      <c r="G52" s="45" t="n">
+        <v>32741.6246877908</v>
+      </c>
+      <c r="H52" s="45" t="n">
+        <v>16047.1920847664</v>
+      </c>
+      <c r="I52" s="46" t="n">
+        <v>0.9612301577628493</v>
+      </c>
+      <c r="J52" s="46" t="n">
+        <v>0.03109042252951388</v>
+      </c>
+      <c r="K52" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="40" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C53" s="39" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D53" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E53" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F53" s="41" t="n">
+        <v>72497.86860120999</v>
+      </c>
+      <c r="G53" s="41" t="n">
+        <v>139592.612210761</v>
+      </c>
+      <c r="H53" s="41" t="n">
+        <v>67094.74360955101</v>
+      </c>
+      <c r="I53" s="42" t="n">
+        <v>0.9254719470253667</v>
+      </c>
+      <c r="J53" s="42" t="n">
+        <v>0.03022837892120145</v>
+      </c>
+      <c r="K53" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
+        <is>
+          <t>MNE</t>
+        </is>
+      </c>
+      <c r="D54" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E54" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F54" s="45" t="n">
+        <v>15076.6513903781</v>
+      </c>
+      <c r="G54" s="45" t="n">
+        <v>28895.3171970071</v>
+      </c>
+      <c r="H54" s="45" t="n">
+        <v>13818.665806629</v>
+      </c>
+      <c r="I54" s="46" t="n">
+        <v>0.9165606770909394</v>
+      </c>
+      <c r="J54" s="46" t="n">
+        <v>0.03001117164607248</v>
+      </c>
+      <c r="K54" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="40" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="C55" s="39" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="D55" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E55" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F55" s="41" t="n">
+        <v>14898.7197394794</v>
+      </c>
+      <c r="G55" s="41" t="n">
+        <v>28443.4127676388</v>
+      </c>
+      <c r="H55" s="41" t="n">
+        <v>13544.6930281594</v>
+      </c>
+      <c r="I55" s="42" t="n">
+        <v>0.9091179151634062</v>
+      </c>
+      <c r="J55" s="42" t="n">
+        <v>0.02982901834752449</v>
+      </c>
+      <c r="K55" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>Marshall Islands</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
+        <is>
+          <t>MHL</t>
+        </is>
+      </c>
+      <c r="D56" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E56" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F56" s="45" t="n">
+        <v>4041.17284358405</v>
+      </c>
+      <c r="G56" s="45" t="n">
+        <v>7660.37695591168</v>
+      </c>
+      <c r="H56" s="45" t="n">
+        <v>3619.20411232763</v>
+      </c>
+      <c r="I56" s="46" t="n">
+        <v>0.8955826074288415</v>
+      </c>
+      <c r="J56" s="46" t="n">
+        <v>0.02949601262089785</v>
+      </c>
+      <c r="K56" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="n">
+        <v>51</v>
+      </c>
+      <c r="B57" s="40" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="C57" s="39" t="inlineStr">
+        <is>
+          <t>TZA</t>
+        </is>
+      </c>
+      <c r="D57" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E57" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F57" s="41" t="n">
+        <v>2059.83740234375</v>
+      </c>
+      <c r="G57" s="41" t="n">
+        <v>3820.61181640625</v>
+      </c>
+      <c r="H57" s="41" t="n">
+        <v>1760.7744140625</v>
+      </c>
+      <c r="I57" s="42" t="n">
+        <v>0.8548123323030419</v>
+      </c>
+      <c r="J57" s="42" t="n">
+        <v>0.028479059015033</v>
+      </c>
+      <c r="K57" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>Korea, Rep.</t>
+        </is>
+      </c>
+      <c r="C58" s="43" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="D58" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E58" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F58" s="45" t="n">
+        <v>30142.4605585814</v>
+      </c>
+      <c r="G58" s="45" t="n">
+        <v>55697.0848086328</v>
+      </c>
+      <c r="H58" s="45" t="n">
+        <v>25554.6242500514</v>
+      </c>
+      <c r="I58" s="46" t="n">
+        <v>0.8477948971812168</v>
+      </c>
+      <c r="J58" s="46" t="n">
+        <v>0.0283018700643447</v>
+      </c>
+      <c r="K58" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="n">
+        <v>53</v>
+      </c>
+      <c r="B59" s="40" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C59" s="39" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="D59" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E59" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F59" s="41" t="n">
+        <v>19329.0062757538</v>
+      </c>
+      <c r="G59" s="41" t="n">
+        <v>35461.4465805872</v>
+      </c>
+      <c r="H59" s="41" t="n">
+        <v>16132.4403048334</v>
+      </c>
+      <c r="I59" s="42" t="n">
+        <v>0.8346233673207426</v>
+      </c>
+      <c r="J59" s="42" t="n">
+        <v>0.02796755011736929</v>
+      </c>
+      <c r="K59" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" s="44" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="C60" s="43" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="D60" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E60" s="44" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F60" s="45" t="n">
+        <v>1649.1482601448</v>
+      </c>
+      <c r="G60" s="45" t="n">
+        <v>2980.37942135501</v>
+      </c>
+      <c r="H60" s="45" t="n">
+        <v>1331.23116121021</v>
+      </c>
+      <c r="I60" s="46" t="n">
+        <v>0.8072234579402364</v>
+      </c>
+      <c r="J60" s="46" t="n">
+        <v>0.02726468198986121</v>
+      </c>
+      <c r="K60" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="n">
+        <v>55</v>
+      </c>
+      <c r="B61" s="40" t="inlineStr">
+        <is>
+          <t>Somalia, Fed. Rep.</t>
+        </is>
+      </c>
+      <c r="C61" s="39" t="inlineStr">
+        <is>
+          <t>SOM</t>
+        </is>
+      </c>
+      <c r="D61" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E61" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F61" s="41" t="n">
+        <v>777.884552733128</v>
+      </c>
+      <c r="G61" s="41" t="n">
+        <v>1403.81389064466</v>
+      </c>
+      <c r="H61" s="41" t="n">
+        <v>625.929337911532</v>
+      </c>
+      <c r="I61" s="42" t="n">
+        <v>0.8046558267705722</v>
+      </c>
+      <c r="J61" s="42" t="n">
+        <v>0.02719829620045155</v>
+      </c>
+      <c r="K61" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="n">
+        <v>56</v>
+      </c>
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
+        <is>
+          <t>IRQ</t>
+        </is>
+      </c>
+      <c r="D62" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E62" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F62" s="45" t="n">
+        <v>6849.3320080035</v>
+      </c>
+      <c r="G62" s="45" t="n">
+        <v>12191.5564658302</v>
+      </c>
+      <c r="H62" s="45" t="n">
+        <v>5342.224457826699</v>
+      </c>
+      <c r="I62" s="46" t="n">
+        <v>0.7799628418631579</v>
+      </c>
+      <c r="J62" s="46" t="n">
+        <v>0.02655521898424285</v>
+      </c>
+      <c r="K62" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="39" t="n">
+        <v>57</v>
+      </c>
+      <c r="B63" s="40" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="C63" s="39" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="D63" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F63" s="41" t="n">
+        <v>24057.927734375</v>
+      </c>
+      <c r="G63" s="41" t="n">
+        <v>42357.98828125</v>
+      </c>
+      <c r="H63" s="41" t="n">
+        <v>18300.060546875</v>
+      </c>
+      <c r="I63" s="42" t="n">
+        <v>0.7606665357435207</v>
+      </c>
+      <c r="J63" s="42" t="n">
+        <v>0.02604673174422323</v>
+      </c>
+      <c r="K63" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" s="44" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="D64" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E64" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F64" s="45" t="n">
+        <v>9902.199180038169</v>
+      </c>
+      <c r="G64" s="45" t="n">
+        <v>17245.8458423118</v>
+      </c>
+      <c r="H64" s="45" t="n">
+        <v>7343.64666227363</v>
+      </c>
+      <c r="I64" s="46" t="n">
+        <v>0.7416177486186784</v>
+      </c>
+      <c r="J64" s="46" t="n">
+        <v>0.0255395223291337</v>
+      </c>
+      <c r="K64" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="39" t="n">
+        <v>59</v>
+      </c>
+      <c r="B65" s="40" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C65" s="39" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="D65" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E65" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F65" s="41" t="n">
+        <v>25473.5672036391</v>
+      </c>
+      <c r="G65" s="41" t="n">
+        <v>44172.0442284906</v>
+      </c>
+      <c r="H65" s="41" t="n">
+        <v>18698.4770248515</v>
+      </c>
+      <c r="I65" s="42" t="n">
+        <v>0.7340344944770938</v>
+      </c>
+      <c r="J65" s="42" t="n">
+        <v>0.02533612903491367</v>
+      </c>
+      <c r="K65" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="B66" s="44" t="inlineStr">
+        <is>
+          <t>Cote d'Ivoire</t>
+        </is>
+      </c>
+      <c r="C66" s="43" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="D66" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E66" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F66" s="45" t="n">
+        <v>4060.03041319294</v>
+      </c>
+      <c r="G66" s="45" t="n">
+        <v>7014.84577693062</v>
+      </c>
+      <c r="H66" s="45" t="n">
+        <v>2954.815363737679</v>
+      </c>
+      <c r="I66" s="46" t="n">
+        <v>0.7277815836393987</v>
+      </c>
+      <c r="J66" s="46" t="n">
+        <v>0.02516777767189571</v>
+      </c>
+      <c r="K66" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="39" t="n">
+        <v>61</v>
+      </c>
+      <c r="B67" s="40" t="inlineStr">
+        <is>
+          <t>Macao SAR, China</t>
+        </is>
+      </c>
+      <c r="C67" s="39" t="inlineStr">
+        <is>
+          <t>MAC</t>
+        </is>
+      </c>
+      <c r="D67" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E67" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F67" s="41" t="n">
+        <v>67994.777526459</v>
+      </c>
+      <c r="G67" s="41" t="n">
+        <v>117098.274845518</v>
+      </c>
+      <c r="H67" s="41" t="n">
+        <v>49103.497319059</v>
+      </c>
+      <c r="I67" s="42" t="n">
+        <v>0.7221657178001828</v>
+      </c>
+      <c r="J67" s="42" t="n">
+        <v>0.02501608144635203</v>
+      </c>
+      <c r="K67" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="B68" s="44" t="inlineStr">
+        <is>
+          <t>Congo, Dem. Rep.</t>
+        </is>
+      </c>
+      <c r="C68" s="43" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E68" s="44" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F68" s="45" t="n">
+        <v>953.044643242042</v>
+      </c>
+      <c r="G68" s="45" t="n">
+        <v>1640.56621824278</v>
+      </c>
+      <c r="H68" s="45" t="n">
+        <v>687.521575000738</v>
+      </c>
+      <c r="I68" s="46" t="n">
+        <v>0.7213949313664314</v>
+      </c>
+      <c r="J68" s="46" t="n">
+        <v>0.02499522405891552</v>
+      </c>
+      <c r="K68" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="39" t="n">
+        <v>63</v>
+      </c>
+      <c r="B69" s="40" t="inlineStr">
+        <is>
+          <t>Guinea</t>
+        </is>
+      </c>
+      <c r="C69" s="39" t="inlineStr">
+        <is>
+          <t>GIN</t>
+        </is>
+      </c>
+      <c r="D69" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E69" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F69" s="41" t="n">
+        <v>2473.23418295471</v>
+      </c>
+      <c r="G69" s="41" t="n">
+        <v>4216.85970804544</v>
+      </c>
+      <c r="H69" s="41" t="n">
+        <v>1743.62552509073</v>
+      </c>
+      <c r="I69" s="42" t="n">
+        <v>0.7049981506432461</v>
+      </c>
+      <c r="J69" s="42" t="n">
+        <v>0.02454940419885898</v>
+      </c>
+      <c r="K69" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="43" t="n">
+        <v>64</v>
+      </c>
+      <c r="B70" s="44" t="inlineStr">
+        <is>
+          <t>St. Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="C70" s="43" t="inlineStr">
+        <is>
+          <t>VCT</t>
+        </is>
+      </c>
+      <c r="D70" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E70" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F70" s="45" t="n">
+        <v>11475.3312414531</v>
+      </c>
+      <c r="G70" s="45" t="n">
+        <v>19483.0127638994</v>
+      </c>
+      <c r="H70" s="45" t="n">
+        <v>8007.681522446303</v>
+      </c>
+      <c r="I70" s="46" t="n">
+        <v>0.6978170262762982</v>
+      </c>
+      <c r="J70" s="46" t="n">
+        <v>0.0243528631394736</v>
+      </c>
+      <c r="K70" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="n">
+        <v>65</v>
+      </c>
+      <c r="B71" s="40" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C71" s="39" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="D71" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E71" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F71" s="41" t="n">
+        <v>13288.7481561137</v>
+      </c>
+      <c r="G71" s="41" t="n">
+        <v>22431.7518380848</v>
+      </c>
+      <c r="H71" s="41" t="n">
+        <v>9143.003681971102</v>
+      </c>
+      <c r="I71" s="42" t="n">
+        <v>0.6880259580933301</v>
+      </c>
+      <c r="J71" s="42" t="n">
+        <v>0.02408360782283814</v>
+      </c>
+      <c r="K71" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="43" t="n">
+        <v>66</v>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>Egypt, Arab Rep.</t>
+        </is>
+      </c>
+      <c r="C72" s="43" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E72" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F72" s="45" t="n">
+        <v>10250.376550149</v>
+      </c>
+      <c r="G72" s="45" t="n">
+        <v>17265.1488604617</v>
+      </c>
+      <c r="H72" s="45" t="n">
+        <v>7014.772310312701</v>
+      </c>
+      <c r="I72" s="46" t="n">
+        <v>0.6843428898434696</v>
+      </c>
+      <c r="J72" s="46" t="n">
+        <v>0.0239819370696861</v>
+      </c>
+      <c r="K72" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" s="40" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="C73" s="39" t="inlineStr">
+        <is>
+          <t>BFA</t>
+        </is>
+      </c>
+      <c r="D73" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E73" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F73" s="41" t="n">
+        <v>1561.83310184915</v>
+      </c>
+      <c r="G73" s="41" t="n">
+        <v>2624.82858270803</v>
+      </c>
+      <c r="H73" s="41" t="n">
+        <v>1062.99548085888</v>
+      </c>
+      <c r="I73" s="42" t="n">
+        <v>0.6806076011581099</v>
+      </c>
+      <c r="J73" s="42" t="n">
+        <v>0.02387860779771667</v>
+      </c>
+      <c r="K73" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="43" t="n">
+        <v>68</v>
+      </c>
+      <c r="B74" s="44" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C74" s="43" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D74" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E74" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F74" s="45" t="n">
+        <v>11183.2911819793</v>
+      </c>
+      <c r="G74" s="45" t="n">
+        <v>18778.6482631901</v>
+      </c>
+      <c r="H74" s="45" t="n">
+        <v>7595.357081210801</v>
+      </c>
+      <c r="I74" s="46" t="n">
+        <v>0.6791701081207581</v>
+      </c>
+      <c r="J74" s="46" t="n">
+        <v>0.02383878400947914</v>
+      </c>
+      <c r="K74" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="39" t="n">
+        <v>69</v>
+      </c>
+      <c r="B75" s="40" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR, China</t>
+        </is>
+      </c>
+      <c r="C75" s="39" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="D75" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E75" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F75" s="41" t="n">
+        <v>41570.5634425877</v>
+      </c>
+      <c r="G75" s="41" t="n">
+        <v>68724.55658657561</v>
+      </c>
+      <c r="H75" s="41" t="n">
+        <v>27153.99314398791</v>
+      </c>
+      <c r="I75" s="42" t="n">
+        <v>0.6532024320885081</v>
+      </c>
+      <c r="J75" s="42" t="n">
+        <v>0.02311372492896768</v>
+      </c>
+      <c r="K75" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="B76" s="44" t="inlineStr">
+        <is>
+          <t>Mozambique</t>
+        </is>
+      </c>
+      <c r="C76" s="43" t="inlineStr">
+        <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="D76" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E76" s="44" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F76" s="45" t="n">
+        <v>883.239121472194</v>
+      </c>
+      <c r="G76" s="45" t="n">
+        <v>1450.95955248858</v>
+      </c>
+      <c r="H76" s="45" t="n">
+        <v>567.7204310163859</v>
+      </c>
+      <c r="I76" s="46" t="n">
+        <v>0.6427709294286043</v>
+      </c>
+      <c r="J76" s="46" t="n">
+        <v>0.02281939570906788</v>
+      </c>
+      <c r="K76" s="43" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="n">
+        <v>71</v>
+      </c>
+      <c r="B77" s="40" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="C77" s="39" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D77" s="40" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E77" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F77" s="41" t="n">
+        <v>5810.05322265625</v>
+      </c>
+      <c r="G77" s="41" t="n">
+        <v>9495.4052734375</v>
+      </c>
+      <c r="H77" s="41" t="n">
+        <v>3685.35205078125</v>
+      </c>
+      <c r="I77" s="42" t="n">
+        <v>0.6343060742387441</v>
+      </c>
+      <c r="J77" s="42" t="n">
+        <v>0.02257924209208562</v>
+      </c>
+      <c r="K77" s="39" t="inlineStr">
+        <is>
+          <t>Acima</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="43" t="n">
+        <v>72</v>
+      </c>
+      <c r="B78" s="44" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="D78" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E78" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F78" s="45" t="n">
+        <v>25485.1613028986</v>
+      </c>
+      <c r="G78" s="45" t="n">
+        <v>41604.3226612806</v>
+      </c>
+      <c r="H78" s="45" t="n">
+        <v>16119.161358382</v>
+      </c>
+      <c r="I78" s="46" t="n">
+        <v>0.6324920280786555</v>
+      </c>
+      <c r="J78" s="46" t="n">
+        <v>0.02252762192459801</v>
+      </c>
+      <c r="K78" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="39" t="n">
+        <v>73</v>
+      </c>
+      <c r="B79" s="40" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C79" s="39" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="D79" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E79" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F79" s="41" t="n">
+        <v>18907.3458745755</v>
+      </c>
+      <c r="G79" s="41" t="n">
+        <v>30863.4223155169</v>
+      </c>
+      <c r="H79" s="41" t="n">
+        <v>11956.0764409414</v>
+      </c>
+      <c r="I79" s="42" t="n">
+        <v>0.6323508608904542</v>
+      </c>
+      <c r="J79" s="42" t="n">
+        <v>0.02252360260086372</v>
+      </c>
+      <c r="K79" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" s="44" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="D80" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E80" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F80" s="45" t="n">
+        <v>3674.08592758409</v>
+      </c>
+      <c r="G80" s="45" t="n">
+        <v>5995.40177895632</v>
+      </c>
+      <c r="H80" s="45" t="n">
+        <v>2321.315851372231</v>
+      </c>
+      <c r="I80" s="46" t="n">
+        <v>0.6318077195594118</v>
+      </c>
+      <c r="J80" s="46" t="n">
+        <v>0.02250813514169647</v>
+      </c>
+      <c r="K80" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" s="40" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="C81" s="39" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="D81" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E81" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F81" s="41" t="n">
+        <v>25255.8711300567</v>
+      </c>
+      <c r="G81" s="41" t="n">
+        <v>41160.6419140983</v>
+      </c>
+      <c r="H81" s="41" t="n">
+        <v>15904.7707840416</v>
+      </c>
+      <c r="I81" s="42" t="n">
+        <v>0.6297454838179597</v>
+      </c>
+      <c r="J81" s="42" t="n">
+        <v>0.0224493624602724</v>
+      </c>
+      <c r="K81" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="n">
+        <v>76</v>
+      </c>
+      <c r="B82" s="44" t="inlineStr">
+        <is>
+          <t>Eswatini</t>
+        </is>
+      </c>
+      <c r="C82" s="43" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="D82" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E82" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F82" s="45" t="n">
+        <v>6578.30152863605</v>
+      </c>
+      <c r="G82" s="45" t="n">
+        <v>10706.7778049468</v>
+      </c>
+      <c r="H82" s="45" t="n">
+        <v>4128.47627631075</v>
+      </c>
+      <c r="I82" s="46" t="n">
+        <v>0.6275900030333137</v>
+      </c>
+      <c r="J82" s="46" t="n">
+        <v>0.0223878564171105</v>
+      </c>
+      <c r="K82" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="39" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" s="40" t="inlineStr">
+        <is>
+          <t>Seychelles</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="inlineStr">
+        <is>
+          <t>SYC</t>
+        </is>
+      </c>
+      <c r="D83" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E83" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F83" s="41" t="n">
+        <v>18825.2206936189</v>
+      </c>
+      <c r="G83" s="41" t="n">
+        <v>30638.7217194523</v>
+      </c>
+      <c r="H83" s="41" t="n">
+        <v>11813.5010258334</v>
+      </c>
+      <c r="I83" s="42" t="n">
+        <v>0.6275358583093673</v>
+      </c>
+      <c r="J83" s="42" t="n">
+        <v>0.02238631041163641</v>
+      </c>
+      <c r="K83" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="B84" s="44" t="inlineStr">
+        <is>
+          <t>Naoero</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>NRU</t>
+        </is>
+      </c>
+      <c r="D84" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E84" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F84" s="45" t="n">
+        <v>7527.37549326971</v>
+      </c>
+      <c r="G84" s="45" t="n">
+        <v>12134.8920885013</v>
+      </c>
+      <c r="H84" s="45" t="n">
+        <v>4607.516595231589</v>
+      </c>
+      <c r="I84" s="46" t="n">
+        <v>0.6121013358973799</v>
+      </c>
+      <c r="J84" s="46" t="n">
+        <v>0.02194359116930999</v>
+      </c>
+      <c r="K84" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="39" t="n">
+        <v>79</v>
+      </c>
+      <c r="B85" s="40" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="C85" s="39" t="inlineStr">
+        <is>
+          <t>MDV</t>
+        </is>
+      </c>
+      <c r="D85" s="40" t="inlineStr">
+        <is>
+          <t>South Asia</t>
+        </is>
+      </c>
+      <c r="E85" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F85" s="41" t="n">
+        <v>15316.1192814998</v>
+      </c>
+      <c r="G85" s="41" t="n">
+        <v>24401.3159253635</v>
+      </c>
+      <c r="H85" s="41" t="n">
+        <v>9085.196643863699</v>
+      </c>
+      <c r="I85" s="42" t="n">
+        <v>0.5931787600294824</v>
+      </c>
+      <c r="J85" s="42" t="n">
+        <v>0.0213952674703406</v>
+      </c>
+      <c r="K85" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="B86" s="44" t="inlineStr">
+        <is>
+          <t>Nicaragua</t>
+        </is>
+      </c>
+      <c r="C86" s="43" t="inlineStr">
+        <is>
+          <t>NIC</t>
+        </is>
+      </c>
+      <c r="D86" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E86" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F86" s="45" t="n">
+        <v>5000.61145616409</v>
+      </c>
+      <c r="G86" s="45" t="n">
+        <v>7933.48888006412</v>
+      </c>
+      <c r="H86" s="45" t="n">
+        <v>2932.87742390003</v>
+      </c>
+      <c r="I86" s="46" t="n">
+        <v>0.5865037605120806</v>
+      </c>
+      <c r="J86" s="46" t="n">
+        <v>0.02120036029259276</v>
+      </c>
+      <c r="K86" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="39" t="n">
+        <v>81</v>
+      </c>
+      <c r="B87" s="40" t="inlineStr">
+        <is>
+          <t>St. Kitts and Nevis</t>
+        </is>
+      </c>
+      <c r="C87" s="39" t="inlineStr">
+        <is>
+          <t>KNA</t>
+        </is>
+      </c>
+      <c r="D87" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E87" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F87" s="41" t="n">
+        <v>19927.1818314137</v>
+      </c>
+      <c r="G87" s="41" t="n">
+        <v>31427.6630825717</v>
+      </c>
+      <c r="H87" s="41" t="n">
+        <v>11500.481251158</v>
+      </c>
+      <c r="I87" s="42" t="n">
+        <v>0.5771253230112225</v>
+      </c>
+      <c r="J87" s="42" t="n">
+        <v>0.02092518720530379</v>
+      </c>
+      <c r="K87" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="43" t="n">
+        <v>82</v>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="C88" s="43" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="D88" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E88" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F88" s="45" t="n">
+        <v>2383.87611741089</v>
+      </c>
+      <c r="G88" s="45" t="n">
+        <v>3742.25646316492</v>
+      </c>
+      <c r="H88" s="45" t="n">
+        <v>1358.38034575403</v>
+      </c>
+      <c r="I88" s="46" t="n">
+        <v>0.569820023713882</v>
+      </c>
+      <c r="J88" s="46" t="n">
+        <v>0.02070975779069006</v>
+      </c>
+      <c r="K88" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="39" t="n">
+        <v>83</v>
+      </c>
+      <c r="B89" s="40" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="C89" s="39" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="D89" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E89" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F89" s="41" t="n">
+        <v>2639.04370114641</v>
+      </c>
+      <c r="G89" s="41" t="n">
+        <v>4116.2151559488</v>
+      </c>
+      <c r="H89" s="41" t="n">
+        <v>1477.17145480239</v>
+      </c>
+      <c r="I89" s="42" t="n">
+        <v>0.5597373981191374</v>
+      </c>
+      <c r="J89" s="42" t="n">
+        <v>0.02041084933410842</v>
+      </c>
+      <c r="K89" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="43" t="n">
+        <v>84</v>
+      </c>
+      <c r="B90" s="44" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="D90" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E90" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F90" s="45" t="n">
+        <v>7780.27177685599</v>
+      </c>
+      <c r="G90" s="45" t="n">
+        <v>12050.028265702</v>
+      </c>
+      <c r="H90" s="45" t="n">
+        <v>4269.75648884601</v>
+      </c>
+      <c r="I90" s="46" t="n">
+        <v>0.5487927171833862</v>
+      </c>
+      <c r="J90" s="46" t="n">
+        <v>0.02008428954965402</v>
+      </c>
+      <c r="K90" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="39" t="n">
+        <v>85</v>
+      </c>
+      <c r="B91" s="40" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="C91" s="39" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="D91" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E91" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F91" s="41" t="n">
+        <v>31949.2963145034</v>
+      </c>
+      <c r="G91" s="41" t="n">
+        <v>49292.4878713208</v>
+      </c>
+      <c r="H91" s="41" t="n">
+        <v>17343.1915568174</v>
+      </c>
+      <c r="I91" s="42" t="n">
+        <v>0.5428348526394444</v>
+      </c>
+      <c r="J91" s="42" t="n">
+        <v>0.0199055958159271</v>
+      </c>
+      <c r="K91" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="43" t="n">
+        <v>86</v>
+      </c>
+      <c r="B92" s="44" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C92" s="43" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="D92" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E92" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F92" s="45" t="n">
+        <v>3668.77938852508</v>
+      </c>
+      <c r="G92" s="45" t="n">
+        <v>5617.25078028458</v>
+      </c>
+      <c r="H92" s="45" t="n">
+        <v>1948.4713917595</v>
+      </c>
+      <c r="I92" s="46" t="n">
+        <v>0.5310952732273235</v>
+      </c>
+      <c r="J92" s="46" t="n">
+        <v>0.01955155563151023</v>
+      </c>
+      <c r="K92" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="39" t="n">
+        <v>87</v>
+      </c>
+      <c r="B93" s="40" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C93" s="39" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="D93" s="40" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E93" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F93" s="41" t="n">
+        <v>31771.2115906733</v>
+      </c>
+      <c r="G93" s="41" t="n">
+        <v>48196.6345176562</v>
+      </c>
+      <c r="H93" s="41" t="n">
+        <v>16425.4229269829</v>
+      </c>
+      <c r="I93" s="42" t="n">
+        <v>0.5169907631663855</v>
+      </c>
+      <c r="J93" s="42" t="n">
+        <v>0.01912275141645203</v>
+      </c>
+      <c r="K93" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="43" t="n">
+        <v>88</v>
+      </c>
+      <c r="B94" s="44" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="D94" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E94" s="44" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F94" s="45" t="n">
+        <v>1238.58780880353</v>
+      </c>
+      <c r="G94" s="45" t="n">
+        <v>1860.54858272608</v>
+      </c>
+      <c r="H94" s="45" t="n">
+        <v>621.9607739225501</v>
+      </c>
+      <c r="I94" s="46" t="n">
+        <v>0.502153153375021</v>
+      </c>
+      <c r="J94" s="46" t="n">
+        <v>0.01866753236900465</v>
+      </c>
+      <c r="K94" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="39" t="n">
+        <v>89</v>
+      </c>
+      <c r="B95" s="40" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C95" s="39" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="D95" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F95" s="41" t="n">
+        <v>32833.9045969454</v>
+      </c>
+      <c r="G95" s="41" t="n">
+        <v>49091.0184405902</v>
+      </c>
+      <c r="H95" s="41" t="n">
+        <v>16257.11384364479</v>
+      </c>
+      <c r="I95" s="42" t="n">
+        <v>0.4951319084102237</v>
+      </c>
+      <c r="J95" s="42" t="n">
+        <v>0.01845062195299429</v>
+      </c>
+      <c r="K95" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="B96" s="44" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="inlineStr">
+        <is>
+          <t>FJI</t>
+        </is>
+      </c>
+      <c r="D96" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E96" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F96" s="45" t="n">
+        <v>9361.4641667422</v>
+      </c>
+      <c r="G96" s="45" t="n">
+        <v>13961.1183693541</v>
+      </c>
+      <c r="H96" s="45" t="n">
+        <v>4599.6542026119</v>
+      </c>
+      <c r="I96" s="46" t="n">
+        <v>0.4913391880463274</v>
+      </c>
+      <c r="J96" s="46" t="n">
+        <v>0.0183330469593761</v>
+      </c>
+      <c r="K96" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="39" t="n">
+        <v>91</v>
+      </c>
+      <c r="B97" s="40" t="inlineStr">
+        <is>
+          <t>Kiribati</t>
+        </is>
+      </c>
+      <c r="C97" s="39" t="inlineStr">
+        <is>
+          <t>KIR</t>
+        </is>
+      </c>
+      <c r="D97" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E97" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F97" s="41" t="n">
+        <v>2258.32313744125</v>
+      </c>
+      <c r="G97" s="41" t="n">
+        <v>3363.99521326766</v>
+      </c>
+      <c r="H97" s="41" t="n">
+        <v>1105.67207582641</v>
+      </c>
+      <c r="I97" s="42" t="n">
+        <v>0.4895987015742889</v>
+      </c>
+      <c r="J97" s="42" t="n">
+        <v>0.018278996000755</v>
+      </c>
+      <c r="K97" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="43" t="n">
+        <v>92</v>
+      </c>
+      <c r="B98" s="44" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="C98" s="43" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="D98" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E98" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F98" s="45" t="n">
+        <v>3170.03494689265</v>
+      </c>
+      <c r="G98" s="45" t="n">
+        <v>4668.54167658726</v>
+      </c>
+      <c r="H98" s="45" t="n">
+        <v>1498.506729694609</v>
+      </c>
+      <c r="I98" s="46" t="n">
+        <v>0.4727098454114787</v>
+      </c>
+      <c r="J98" s="46" t="n">
+        <v>0.01775135782681536</v>
+      </c>
+      <c r="K98" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="39" t="n">
+        <v>93</v>
+      </c>
+      <c r="B99" s="40" t="inlineStr">
+        <is>
+          <t>Samoa</t>
+        </is>
+      </c>
+      <c r="C99" s="39" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="D99" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F99" s="41" t="n">
+        <v>5426.13899111084</v>
+      </c>
+      <c r="G99" s="41" t="n">
+        <v>7963.42749052153</v>
+      </c>
+      <c r="H99" s="41" t="n">
+        <v>2537.28849941069</v>
+      </c>
+      <c r="I99" s="42" t="n">
+        <v>0.4676047745122827</v>
+      </c>
+      <c r="J99" s="42" t="n">
+        <v>0.01759072912762694</v>
+      </c>
+      <c r="K99" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="43" t="n">
+        <v>94</v>
+      </c>
+      <c r="B100" s="44" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C100" s="43" t="inlineStr">
+        <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="D100" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E100" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F100" s="45" t="n">
+        <v>9802.81408202125</v>
+      </c>
+      <c r="G100" s="45" t="n">
+        <v>14319.2406558299</v>
+      </c>
+      <c r="H100" s="45" t="n">
+        <v>4516.426573808651</v>
+      </c>
+      <c r="I100" s="46" t="n">
+        <v>0.4607275559874136</v>
+      </c>
+      <c r="J100" s="46" t="n">
+        <v>0.01737349534900767</v>
+      </c>
+      <c r="K100" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="39" t="n">
+        <v>95</v>
+      </c>
+      <c r="B101" s="40" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="C101" s="39" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="D101" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F101" s="41" t="n">
+        <v>8926.157717863731</v>
+      </c>
+      <c r="G101" s="41" t="n">
+        <v>12986.5241144632</v>
+      </c>
+      <c r="H101" s="41" t="n">
+        <v>4060.366396599469</v>
+      </c>
+      <c r="I101" s="42" t="n">
+        <v>0.4548840077599732</v>
+      </c>
+      <c r="J101" s="42" t="n">
+        <v>0.01718814401334323</v>
+      </c>
+      <c r="K101" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="43" t="n">
+        <v>96</v>
+      </c>
+      <c r="B102" s="44" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="C102" s="43" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D102" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E102" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F102" s="45" t="n">
+        <v>3064.83667344612</v>
+      </c>
+      <c r="G102" s="45" t="n">
+        <v>4456.23105962118</v>
+      </c>
+      <c r="H102" s="45" t="n">
+        <v>1391.39438617506</v>
+      </c>
+      <c r="I102" s="46" t="n">
+        <v>0.4539864711976864</v>
+      </c>
+      <c r="J102" s="46" t="n">
+        <v>0.01715961213969264</v>
+      </c>
+      <c r="K102" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="39" t="n">
+        <v>97</v>
+      </c>
+      <c r="B103" s="40" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="C103" s="39" t="inlineStr">
+        <is>
+          <t>TGO</t>
+        </is>
+      </c>
+      <c r="D103" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F103" s="41" t="n">
+        <v>2407.5857838237</v>
+      </c>
+      <c r="G103" s="41" t="n">
+        <v>3485.98184512074</v>
+      </c>
+      <c r="H103" s="41" t="n">
+        <v>1078.39606129704</v>
+      </c>
+      <c r="I103" s="42" t="n">
+        <v>0.4479159449032568</v>
+      </c>
+      <c r="J103" s="42" t="n">
+        <v>0.01696619306503</v>
+      </c>
+      <c r="K103" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="43" t="n">
+        <v>98</v>
+      </c>
+      <c r="B104" s="44" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="C104" s="43" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+      <c r="D104" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E104" s="44" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F104" s="45" t="n">
+        <v>2196.28134480717</v>
+      </c>
+      <c r="G104" s="45" t="n">
+        <v>3176.23681292996</v>
+      </c>
+      <c r="H104" s="45" t="n">
+        <v>979.9554681227896</v>
+      </c>
+      <c r="I104" s="46" t="n">
+        <v>0.4461884951305399</v>
+      </c>
+      <c r="J104" s="46" t="n">
+        <v>0.01691101158702102</v>
+      </c>
+      <c r="K104" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="39" t="n">
+        <v>99</v>
+      </c>
+      <c r="B105" s="40" t="inlineStr">
+        <is>
+          <t>Tuvalu</t>
+        </is>
+      </c>
+      <c r="C105" s="39" t="inlineStr">
+        <is>
+          <t>TUV</t>
+        </is>
+      </c>
+      <c r="D105" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F105" s="41" t="n">
+        <v>3998.4360743816</v>
+      </c>
+      <c r="G105" s="41" t="n">
+        <v>5776.07849384845</v>
+      </c>
+      <c r="H105" s="41" t="n">
+        <v>1777.64241946685</v>
+      </c>
+      <c r="I105" s="42" t="n">
+        <v>0.4445844291112697</v>
+      </c>
+      <c r="J105" s="42" t="n">
+        <v>0.01685971510093665</v>
+      </c>
+      <c r="K105" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="B106" s="44" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="C106" s="43" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="D106" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E106" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F106" s="45" t="n">
+        <v>7625.90515918892</v>
+      </c>
+      <c r="G106" s="45" t="n">
+        <v>11000.5345220728</v>
+      </c>
+      <c r="H106" s="45" t="n">
+        <v>3374.629362883879</v>
+      </c>
+      <c r="I106" s="46" t="n">
+        <v>0.4425218111737965</v>
+      </c>
+      <c r="J106" s="46" t="n">
+        <v>0.01679367460093939</v>
+      </c>
+      <c r="K106" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="39" t="n">
+        <v>101</v>
+      </c>
+      <c r="B107" s="40" t="inlineStr">
+        <is>
+          <t>Grenada</t>
+        </is>
+      </c>
+      <c r="C107" s="39" t="inlineStr">
+        <is>
+          <t>GRD</t>
+        </is>
+      </c>
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F107" s="41" t="n">
+        <v>12726.5266219464</v>
+      </c>
+      <c r="G107" s="41" t="n">
+        <v>18240.9934237926</v>
+      </c>
+      <c r="H107" s="41" t="n">
+        <v>5514.4668018462</v>
+      </c>
+      <c r="I107" s="42" t="n">
+        <v>0.4333049358759613</v>
+      </c>
+      <c r="J107" s="42" t="n">
+        <v>0.01649746484096903</v>
+      </c>
+      <c r="K107" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="43" t="n">
+        <v>102</v>
+      </c>
+      <c r="B108" s="44" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="C108" s="43" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="D108" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E108" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F108" s="45" t="n">
+        <v>4714.86701000971</v>
+      </c>
+      <c r="G108" s="45" t="n">
+        <v>6726.16685066658</v>
+      </c>
+      <c r="H108" s="45" t="n">
+        <v>2011.29984065687</v>
+      </c>
+      <c r="I108" s="46" t="n">
+        <v>0.4265867597934068</v>
+      </c>
+      <c r="J108" s="46" t="n">
+        <v>0.0162804098196232</v>
+      </c>
+      <c r="K108" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="39" t="n">
+        <v>103</v>
+      </c>
+      <c r="B109" s="40" t="inlineStr">
+        <is>
+          <t>Guinea-Bissau</t>
+        </is>
+      </c>
+      <c r="C109" s="39" t="inlineStr">
+        <is>
+          <t>GNB</t>
+        </is>
+      </c>
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F109" s="41" t="n">
+        <v>2002.40206880451</v>
+      </c>
+      <c r="G109" s="41" t="n">
+        <v>2814.08355940327</v>
+      </c>
+      <c r="H109" s="41" t="n">
+        <v>811.6814905987601</v>
+      </c>
+      <c r="I109" s="42" t="n">
+        <v>0.4053539013188079</v>
+      </c>
+      <c r="J109" s="42" t="n">
+        <v>0.01558793287233806</v>
+      </c>
+      <c r="K109" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="n">
+        <v>104</v>
+      </c>
+      <c r="B110" s="52" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D110" s="52" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E110" s="52" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F110" s="53" t="n">
+        <v>14259.3664089322</v>
+      </c>
+      <c r="G110" s="53" t="n">
+        <v>20024.6968256903</v>
+      </c>
+      <c r="H110" s="53" t="n">
+        <v>5765.330416758099</v>
+      </c>
+      <c r="I110" s="54" t="n">
+        <v>0.4043188351725531</v>
+      </c>
+      <c r="J110" s="54" t="n">
+        <v>0.01555392104535014</v>
+      </c>
+      <c r="K110" s="51" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="39" t="n">
+        <v>105</v>
+      </c>
+      <c r="B111" s="40" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="C111" s="39" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="D111" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F111" s="41" t="n">
+        <v>38617.8125</v>
+      </c>
+      <c r="G111" s="41" t="n">
+        <v>54103.26171875</v>
+      </c>
+      <c r="H111" s="41" t="n">
+        <v>15485.44921875</v>
+      </c>
+      <c r="I111" s="42" t="n">
+        <v>0.4009923974526004</v>
+      </c>
+      <c r="J111" s="42" t="n">
+        <v>0.01544445348377566</v>
+      </c>
+      <c r="K111" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="B112" s="44" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C112" s="43" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D112" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E112" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F112" s="45" t="n">
+        <v>20005.1385113465</v>
+      </c>
+      <c r="G112" s="45" t="n">
+        <v>27846.5984597239</v>
+      </c>
+      <c r="H112" s="45" t="n">
+        <v>7841.4599483774</v>
+      </c>
+      <c r="I112" s="46" t="n">
+        <v>0.391972289715959</v>
+      </c>
+      <c r="J112" s="46" t="n">
+        <v>0.01514636340358422</v>
+      </c>
+      <c r="K112" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="39" t="n">
+        <v>107</v>
+      </c>
+      <c r="B113" s="40" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="C113" s="39" t="inlineStr">
+        <is>
+          <t>MWI</t>
+        </is>
+      </c>
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F113" s="41" t="n">
+        <v>1176.12385998737</v>
+      </c>
+      <c r="G113" s="41" t="n">
+        <v>1623.02178529282</v>
+      </c>
+      <c r="H113" s="41" t="n">
+        <v>446.8979253054499</v>
+      </c>
+      <c r="I113" s="42" t="n">
+        <v>0.3799752224312913</v>
+      </c>
+      <c r="J113" s="42" t="n">
+        <v>0.01474702291406671</v>
+      </c>
+      <c r="K113" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="n">
+        <v>108</v>
+      </c>
+      <c r="B114" s="44" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C114" s="43" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="D114" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E114" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F114" s="45" t="n">
+        <v>5905.31482781101</v>
+      </c>
+      <c r="G114" s="45" t="n">
+        <v>8145.14808387469</v>
+      </c>
+      <c r="H114" s="45" t="n">
+        <v>2239.83325606368</v>
+      </c>
+      <c r="I114" s="46" t="n">
+        <v>0.3792910829267242</v>
+      </c>
+      <c r="J114" s="46" t="n">
+        <v>0.01472415053888576</v>
+      </c>
+      <c r="K114" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="47" t="n">
+        <v>109</v>
+      </c>
+      <c r="B115" s="48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C115" s="47" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D115" s="48" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E115" s="48" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F115" s="49" t="n">
+        <v>56505.4468784112</v>
+      </c>
+      <c r="G115" s="49" t="n">
+        <v>76931.3106990408</v>
+      </c>
+      <c r="H115" s="49" t="n">
+        <v>20425.86382062959</v>
+      </c>
+      <c r="I115" s="50" t="n">
+        <v>0.3614848647172388</v>
+      </c>
+      <c r="J115" s="50" t="n">
+        <v>0.01412500637600944</v>
+      </c>
+      <c r="K115" s="47" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="B116" s="44" t="inlineStr">
+        <is>
+          <t>Dominica</t>
+        </is>
+      </c>
+      <c r="C116" s="43" t="inlineStr">
+        <is>
+          <t>DMA</t>
+        </is>
+      </c>
+      <c r="D116" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E116" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F116" s="45" t="n">
+        <v>14398.0017636834</v>
+      </c>
+      <c r="G116" s="45" t="n">
+        <v>19409.2900700194</v>
+      </c>
+      <c r="H116" s="45" t="n">
+        <v>5011.288306336</v>
+      </c>
+      <c r="I116" s="46" t="n">
+        <v>0.3480544306485747</v>
+      </c>
+      <c r="J116" s="46" t="n">
+        <v>0.01366812956831343</v>
+      </c>
+      <c r="K116" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="39" t="n">
+        <v>111</v>
+      </c>
+      <c r="B117" s="40" t="inlineStr">
+        <is>
+          <t>St. Lucia</t>
+        </is>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>LCA</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F117" s="41" t="n">
+        <v>18344.5919258071</v>
+      </c>
+      <c r="G117" s="41" t="n">
+        <v>24502.9628641276</v>
+      </c>
+      <c r="H117" s="41" t="n">
+        <v>6158.370938320499</v>
+      </c>
+      <c r="I117" s="42" t="n">
+        <v>0.3357049839662514</v>
+      </c>
+      <c r="J117" s="42" t="n">
+        <v>0.01324417506206088</v>
+      </c>
+      <c r="K117" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="n">
+        <v>112</v>
+      </c>
+      <c r="B118" s="44" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C118" s="43" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="D118" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E118" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F118" s="45" t="n">
+        <v>9752.02442335824</v>
+      </c>
+      <c r="G118" s="45" t="n">
+        <v>13017.6340422977</v>
+      </c>
+      <c r="H118" s="45" t="n">
+        <v>3265.609618939459</v>
+      </c>
+      <c r="I118" s="46" t="n">
+        <v>0.3348647908548719</v>
+      </c>
+      <c r="J118" s="46" t="n">
+        <v>0.01321519559320139</v>
+      </c>
+      <c r="K118" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="39" t="n">
+        <v>113</v>
+      </c>
+      <c r="B119" s="40" t="inlineStr">
+        <is>
+          <t>Chad</t>
+        </is>
+      </c>
+      <c r="C119" s="39" t="inlineStr">
+        <is>
+          <t>TCD</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F119" s="41" t="n">
+        <v>1878.58578618822</v>
+      </c>
+      <c r="G119" s="41" t="n">
+        <v>2480.50962500924</v>
+      </c>
+      <c r="H119" s="41" t="n">
+        <v>601.9238388210201</v>
+      </c>
+      <c r="I119" s="42" t="n">
+        <v>0.3204132828250368</v>
+      </c>
+      <c r="J119" s="42" t="n">
+        <v>0.01271399794961381</v>
+      </c>
+      <c r="K119" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="n">
+        <v>114</v>
+      </c>
+      <c r="B120" s="44" t="inlineStr">
+        <is>
+          <t>Sao Tome and Principe</t>
+        </is>
+      </c>
+      <c r="C120" s="43" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="D120" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E120" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F120" s="45" t="n">
+        <v>4161.63833167542</v>
+      </c>
+      <c r="G120" s="45" t="n">
+        <v>5459.21311766335</v>
+      </c>
+      <c r="H120" s="45" t="n">
+        <v>1297.57478598793</v>
+      </c>
+      <c r="I120" s="46" t="n">
+        <v>0.3117942220283096</v>
+      </c>
+      <c r="J120" s="46" t="n">
+        <v>0.01241257878460988</v>
+      </c>
+      <c r="K120" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="39" t="n">
+        <v>115</v>
+      </c>
+      <c r="B121" s="40" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="C121" s="39" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="D121" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E121" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F121" s="41" t="n">
+        <v>52095.6402740564</v>
+      </c>
+      <c r="G121" s="41" t="n">
+        <v>68064.6854551866</v>
+      </c>
+      <c r="H121" s="41" t="n">
+        <v>15969.0451811302</v>
+      </c>
+      <c r="I121" s="42" t="n">
+        <v>0.3065332357395514</v>
+      </c>
+      <c r="J121" s="42" t="n">
+        <v>0.01222766513198303</v>
+      </c>
+      <c r="K121" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="n">
+        <v>116</v>
+      </c>
+      <c r="B122" s="44" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="C122" s="43" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="D122" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E122" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F122" s="45" t="n">
+        <v>5023.65213216804</v>
+      </c>
+      <c r="G122" s="45" t="n">
+        <v>6559.04321960566</v>
+      </c>
+      <c r="H122" s="45" t="n">
+        <v>1535.39108743762</v>
+      </c>
+      <c r="I122" s="46" t="n">
+        <v>0.3056324456874757</v>
+      </c>
+      <c r="J122" s="46" t="n">
+        <v>0.01219593282921272</v>
+      </c>
+      <c r="K122" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="39" t="n">
+        <v>117</v>
+      </c>
+      <c r="B123" s="40" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="C123" s="39" t="inlineStr">
+        <is>
+          <t>LBR</t>
+        </is>
+      </c>
+      <c r="D123" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E123" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F123" s="41" t="n">
+        <v>1308.15090140274</v>
+      </c>
+      <c r="G123" s="41" t="n">
+        <v>1692.92591135475</v>
+      </c>
+      <c r="H123" s="41" t="n">
+        <v>384.7750099520101</v>
+      </c>
+      <c r="I123" s="42" t="n">
+        <v>0.2941365629450035</v>
+      </c>
+      <c r="J123" s="42" t="n">
+        <v>0.01178911965575136</v>
+      </c>
+      <c r="K123" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="n">
+        <v>118</v>
+      </c>
+      <c r="B124" s="44" t="inlineStr">
+        <is>
+          <t>Lesotho</t>
+        </is>
+      </c>
+      <c r="C124" s="43" t="inlineStr">
+        <is>
+          <t>LSO</t>
+        </is>
+      </c>
+      <c r="D124" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E124" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F124" s="45" t="n">
+        <v>2127.37302160132</v>
+      </c>
+      <c r="G124" s="45" t="n">
+        <v>2720.95737653412</v>
+      </c>
+      <c r="H124" s="45" t="n">
+        <v>593.5843549328001</v>
+      </c>
+      <c r="I124" s="46" t="n">
+        <v>0.2790222254891606</v>
+      </c>
+      <c r="J124" s="46" t="n">
+        <v>0.01124897648188039</v>
+      </c>
+      <c r="K124" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="39" t="n">
+        <v>119</v>
+      </c>
+      <c r="B125" s="40" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="C125" s="39" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="D125" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E125" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F125" s="41" t="n">
+        <v>13857.2588264737</v>
+      </c>
+      <c r="G125" s="41" t="n">
+        <v>17687.2042407934</v>
+      </c>
+      <c r="H125" s="41" t="n">
+        <v>3829.945414319698</v>
+      </c>
+      <c r="I125" s="42" t="n">
+        <v>0.2763855003561564</v>
+      </c>
+      <c r="J125" s="42" t="n">
+        <v>0.01115412374845359</v>
+      </c>
+      <c r="K125" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="B126" s="44" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C126" s="43" t="inlineStr">
+        <is>
+          <t>TTO</t>
+        </is>
+      </c>
+      <c r="D126" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E126" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F126" s="45" t="n">
+        <v>24910.823196152</v>
+      </c>
+      <c r="G126" s="45" t="n">
+        <v>31721.5757411236</v>
+      </c>
+      <c r="H126" s="45" t="n">
+        <v>6810.752544971601</v>
+      </c>
+      <c r="I126" s="46" t="n">
+        <v>0.2734053584396867</v>
+      </c>
+      <c r="J126" s="46" t="n">
+        <v>0.01104669161906791</v>
+      </c>
+      <c r="K126" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="39" t="n">
+        <v>121</v>
+      </c>
+      <c r="B127" s="40" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C127" s="39" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="D127" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E127" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F127" s="41" t="n">
+        <v>50072.4736462925</v>
+      </c>
+      <c r="G127" s="41" t="n">
+        <v>63362.4612808079</v>
+      </c>
+      <c r="H127" s="41" t="n">
+        <v>13289.9876345154</v>
+      </c>
+      <c r="I127" s="42" t="n">
+        <v>0.2654150407745919</v>
+      </c>
+      <c r="J127" s="42" t="n">
+        <v>0.01075745724864374</v>
+      </c>
+      <c r="K127" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="n">
+        <v>122</v>
+      </c>
+      <c r="B128" s="44" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C128" s="43" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="D128" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E128" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F128" s="45" t="n">
+        <v>47581.2285345879</v>
+      </c>
+      <c r="G128" s="45" t="n">
+        <v>60194.0633547961</v>
+      </c>
+      <c r="H128" s="45" t="n">
+        <v>12612.8348202082</v>
+      </c>
+      <c r="I128" s="46" t="n">
+        <v>0.2650800580115251</v>
+      </c>
+      <c r="J128" s="46" t="n">
+        <v>0.01074529346691699</v>
+      </c>
+      <c r="K128" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="39" t="n">
+        <v>123</v>
+      </c>
+      <c r="B129" s="40" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C129" s="39" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="D129" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E129" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F129" s="41" t="n">
+        <v>56452.8695506734</v>
+      </c>
+      <c r="G129" s="41" t="n">
+        <v>71378.4856331012</v>
+      </c>
+      <c r="H129" s="41" t="n">
+        <v>14925.6160824278</v>
+      </c>
+      <c r="I129" s="42" t="n">
+        <v>0.2643907422461531</v>
+      </c>
+      <c r="J129" s="42" t="n">
+        <v>0.01072025358856088</v>
+      </c>
+      <c r="K129" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="43" t="n">
+        <v>124</v>
+      </c>
+      <c r="B130" s="44" t="inlineStr">
+        <is>
+          <t>Timor-Leste</t>
+        </is>
+      </c>
+      <c r="C130" s="43" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="D130" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E130" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F130" s="45" t="n">
+        <v>3264.94647161828</v>
+      </c>
+      <c r="G130" s="45" t="n">
+        <v>4109.9044785289</v>
+      </c>
+      <c r="H130" s="45" t="n">
+        <v>844.9580069106196</v>
+      </c>
+      <c r="I130" s="46" t="n">
+        <v>0.2587968943000201</v>
+      </c>
+      <c r="J130" s="46" t="n">
+        <v>0.01051656985830185</v>
+      </c>
+      <c r="K130" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="39" t="n">
+        <v>125</v>
+      </c>
+      <c r="B131" s="40" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C131" s="39" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="D131" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E131" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F131" s="41" t="n">
+        <v>50191.7219389611</v>
+      </c>
+      <c r="G131" s="41" t="n">
+        <v>62823.7736648822</v>
+      </c>
+      <c r="H131" s="41" t="n">
+        <v>12632.0517259211</v>
+      </c>
+      <c r="I131" s="42" t="n">
+        <v>0.2516759983107002</v>
+      </c>
+      <c r="J131" s="42" t="n">
+        <v>0.01025602948448578</v>
+      </c>
+      <c r="K131" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="43" t="n">
+        <v>126</v>
+      </c>
+      <c r="B132" s="44" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="C132" s="43" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="D132" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E132" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F132" s="45" t="n">
+        <v>58101.4809549972</v>
+      </c>
+      <c r="G132" s="45" t="n">
+        <v>72723.2747867992</v>
+      </c>
+      <c r="H132" s="45" t="n">
+        <v>14621.793831802</v>
+      </c>
+      <c r="I132" s="46" t="n">
+        <v>0.2516595720361652</v>
+      </c>
+      <c r="J132" s="46" t="n">
+        <v>0.01025542684353042</v>
+      </c>
+      <c r="K132" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="39" t="n">
+        <v>127</v>
+      </c>
+      <c r="B133" s="40" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="C133" s="39" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="D133" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E133" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F133" s="41" t="n">
+        <v>68521.3420292943</v>
+      </c>
+      <c r="G133" s="41" t="n">
+        <v>85732.1097535232</v>
+      </c>
+      <c r="H133" s="41" t="n">
+        <v>17210.76772422889</v>
+      </c>
+      <c r="I133" s="42" t="n">
+        <v>0.251173827227011</v>
+      </c>
+      <c r="J133" s="42" t="n">
+        <v>0.01023760260819517</v>
+      </c>
+      <c r="K133" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="43" t="n">
+        <v>128</v>
+      </c>
+      <c r="B134" s="44" t="inlineStr">
+        <is>
+          <t>Iran, Islamic Rep.</t>
+        </is>
+      </c>
+      <c r="C134" s="43" t="inlineStr">
+        <is>
+          <t>IRN</t>
+        </is>
+      </c>
+      <c r="D134" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E134" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F134" s="45" t="n">
+        <v>13519.4501926929</v>
+      </c>
+      <c r="G134" s="45" t="n">
+        <v>16833.7821677117</v>
+      </c>
+      <c r="H134" s="45" t="n">
+        <v>3314.331975018798</v>
+      </c>
+      <c r="I134" s="46" t="n">
+        <v>0.2451528670012153</v>
+      </c>
+      <c r="J134" s="46" t="n">
+        <v>0.0100161155209757</v>
+      </c>
+      <c r="K134" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="39" t="n">
+        <v>129</v>
+      </c>
+      <c r="B135" s="40" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="C135" s="39" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="D135" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E135" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F135" s="41" t="n">
+        <v>8237.365972455969</v>
+      </c>
+      <c r="G135" s="41" t="n">
+        <v>10242.2840471219</v>
+      </c>
+      <c r="H135" s="41" t="n">
+        <v>2004.918074665931</v>
+      </c>
+      <c r="I135" s="42" t="n">
+        <v>0.243393104224088</v>
+      </c>
+      <c r="J135" s="42" t="n">
+        <v>0.009951187795311789</v>
+      </c>
+      <c r="K135" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="n">
+        <v>130</v>
+      </c>
+      <c r="B136" s="44" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C136" s="43" t="inlineStr">
+        <is>
+          <t>DZA</t>
+        </is>
+      </c>
+      <c r="D136" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E136" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F136" s="45" t="n">
+        <v>12835.1814413331</v>
+      </c>
+      <c r="G136" s="45" t="n">
+        <v>15882.7138836328</v>
+      </c>
+      <c r="H136" s="45" t="n">
+        <v>3047.5324422997</v>
+      </c>
+      <c r="I136" s="46" t="n">
+        <v>0.237435867675835</v>
+      </c>
+      <c r="J136" s="46" t="n">
+        <v>0.009730738278408424</v>
+      </c>
+      <c r="K136" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="39" t="n">
+        <v>131</v>
+      </c>
+      <c r="B137" s="40" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C137" s="39" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="D137" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E137" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F137" s="41" t="n">
+        <v>39092.3455202712</v>
+      </c>
+      <c r="G137" s="41" t="n">
+        <v>48232.6651994696</v>
+      </c>
+      <c r="H137" s="41" t="n">
+        <v>9140.319679198401</v>
+      </c>
+      <c r="I137" s="42" t="n">
+        <v>0.2338135396470062</v>
+      </c>
+      <c r="J137" s="42" t="n">
+        <v>0.00959619702602077</v>
+      </c>
+      <c r="K137" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="n">
+        <v>132</v>
+      </c>
+      <c r="B138" s="44" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C138" s="43" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D138" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E138" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F138" s="45" t="n">
+        <v>51788.8439641975</v>
+      </c>
+      <c r="G138" s="45" t="n">
+        <v>63488.4217622523</v>
+      </c>
+      <c r="H138" s="45" t="n">
+        <v>11699.5777980548</v>
+      </c>
+      <c r="I138" s="46" t="n">
+        <v>0.225909228754805</v>
+      </c>
+      <c r="J138" s="46" t="n">
+        <v>0.009301299633234672</v>
+      </c>
+      <c r="K138" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="39" t="n">
+        <v>133</v>
+      </c>
+      <c r="B139" s="40" t="inlineStr">
+        <is>
+          <t>Tonga</t>
+        </is>
+      </c>
+      <c r="C139" s="39" t="inlineStr">
+        <is>
+          <t>TON</t>
+        </is>
+      </c>
+      <c r="D139" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E139" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F139" s="41" t="n">
+        <v>6054.65554234045</v>
+      </c>
+      <c r="G139" s="41" t="n">
+        <v>7412.86641968829</v>
+      </c>
+      <c r="H139" s="41" t="n">
+        <v>1358.21087734784</v>
+      </c>
+      <c r="I139" s="42" t="n">
+        <v>0.2243250450582723</v>
+      </c>
+      <c r="J139" s="42" t="n">
+        <v>0.009241977962539671</v>
+      </c>
+      <c r="K139" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="n">
+        <v>134</v>
+      </c>
+      <c r="B140" s="44" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="C140" s="43" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="D140" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E140" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F140" s="45" t="n">
+        <v>4054.78133246517</v>
+      </c>
+      <c r="G140" s="45" t="n">
+        <v>4945.95640965334</v>
+      </c>
+      <c r="H140" s="45" t="n">
+        <v>891.1750771881702</v>
+      </c>
+      <c r="I140" s="46" t="n">
+        <v>0.2197837575241981</v>
+      </c>
+      <c r="J140" s="46" t="n">
+        <v>0.009071517011497887</v>
+      </c>
+      <c r="K140" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="39" t="n">
+        <v>135</v>
+      </c>
+      <c r="B141" s="40" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="C141" s="39" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="D141" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E141" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F141" s="41" t="n">
+        <v>25136.001691807</v>
+      </c>
+      <c r="G141" s="41" t="n">
+        <v>30620.3075553859</v>
+      </c>
+      <c r="H141" s="41" t="n">
+        <v>5484.305863578902</v>
+      </c>
+      <c r="I141" s="42" t="n">
+        <v>0.2181852917907183</v>
+      </c>
+      <c r="J141" s="42" t="n">
+        <v>0.009011373120056065</v>
+      </c>
+      <c r="K141" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="43" t="n">
+        <v>136</v>
+      </c>
+      <c r="B142" s="44" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C142" s="43" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E142" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F142" s="45" t="n">
+        <v>35115.379514413</v>
+      </c>
+      <c r="G142" s="45" t="n">
+        <v>42576.8139673545</v>
+      </c>
+      <c r="H142" s="45" t="n">
+        <v>7461.434452941503</v>
+      </c>
+      <c r="I142" s="46" t="n">
+        <v>0.2124833778281958</v>
+      </c>
+      <c r="J142" s="46" t="n">
+        <v>0.008796217466519929</v>
+      </c>
+      <c r="K142" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="39" t="n">
+        <v>137</v>
+      </c>
+      <c r="B143" s="40" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C143" s="39" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="D143" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E143" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F143" s="41" t="n">
+        <v>13342.8798828125</v>
+      </c>
+      <c r="G143" s="41" t="n">
+        <v>16155.0732421875</v>
+      </c>
+      <c r="H143" s="41" t="n">
+        <v>2812.193359375</v>
+      </c>
+      <c r="I143" s="42" t="n">
+        <v>0.2107635970700372</v>
+      </c>
+      <c r="J143" s="42" t="n">
+        <v>0.008731133767308608</v>
+      </c>
+      <c r="K143" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="n">
+        <v>138</v>
+      </c>
+      <c r="B144" s="44" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C144" s="43" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="D144" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E144" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F144" s="45" t="n">
+        <v>52234.649280791</v>
+      </c>
+      <c r="G144" s="45" t="n">
+        <v>63051.0467257986</v>
+      </c>
+      <c r="H144" s="45" t="n">
+        <v>10816.3974450076</v>
+      </c>
+      <c r="I144" s="46" t="n">
+        <v>0.2070732280954601</v>
+      </c>
+      <c r="J144" s="46" t="n">
+        <v>0.008591176404729284</v>
+      </c>
+      <c r="K144" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="39" t="n">
+        <v>139</v>
+      </c>
+      <c r="B145" s="40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C145" s="39" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="D145" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E145" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F145" s="41" t="n">
+        <v>40152.1282635641</v>
+      </c>
+      <c r="G145" s="41" t="n">
+        <v>48283.3723959465</v>
+      </c>
+      <c r="H145" s="41" t="n">
+        <v>8131.244132382402</v>
+      </c>
+      <c r="I145" s="42" t="n">
+        <v>0.2025109124728781</v>
+      </c>
+      <c r="J145" s="42" t="n">
+        <v>0.008417584746302165</v>
+      </c>
+      <c r="K145" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="B146" s="44" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="C146" s="43" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="D146" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E146" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F146" s="45" t="n">
+        <v>79150.3962863661</v>
+      </c>
+      <c r="G146" s="45" t="n">
+        <v>95173.4308224367</v>
+      </c>
+      <c r="H146" s="45" t="n">
+        <v>16023.0345360706</v>
+      </c>
+      <c r="I146" s="46" t="n">
+        <v>0.2024378308618855</v>
+      </c>
+      <c r="J146" s="46" t="n">
+        <v>0.008414798949644808</v>
+      </c>
+      <c r="K146" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="39" t="n">
+        <v>141</v>
+      </c>
+      <c r="B147" s="40" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="C147" s="39" t="inlineStr">
+        <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="D147" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E147" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F147" s="41" t="n">
+        <v>4601.68067845787</v>
+      </c>
+      <c r="G147" s="41" t="n">
+        <v>5529.23310016154</v>
+      </c>
+      <c r="H147" s="41" t="n">
+        <v>927.55242170367</v>
+      </c>
+      <c r="I147" s="42" t="n">
+        <v>0.2015681848690367</v>
+      </c>
+      <c r="J147" s="42" t="n">
+        <v>0.008381636519113833</v>
+      </c>
+      <c r="K147" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="43" t="n">
+        <v>142</v>
+      </c>
+      <c r="B148" s="44" t="inlineStr">
+        <is>
+          <t>Palau</t>
+        </is>
+      </c>
+      <c r="C148" s="43" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="D148" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E148" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F148" s="45" t="n">
+        <v>16538.7688424505</v>
+      </c>
+      <c r="G148" s="45" t="n">
+        <v>19698.5947032213</v>
+      </c>
+      <c r="H148" s="45" t="n">
+        <v>3159.825860770801</v>
+      </c>
+      <c r="I148" s="46" t="n">
+        <v>0.1910556880546266</v>
+      </c>
+      <c r="J148" s="46" t="n">
+        <v>0.007978938261220314</v>
+      </c>
+      <c r="K148" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="39" t="n">
+        <v>143</v>
+      </c>
+      <c r="B149" s="40" t="inlineStr">
+        <is>
+          <t>Gambia, The</t>
+        </is>
+      </c>
+      <c r="C149" s="39" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="D149" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E149" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F149" s="41" t="n">
+        <v>2682.47993310133</v>
+      </c>
+      <c r="G149" s="41" t="n">
+        <v>3166.62129644442</v>
+      </c>
+      <c r="H149" s="41" t="n">
+        <v>484.1413633430898</v>
+      </c>
+      <c r="I149" s="42" t="n">
+        <v>0.1804827530558089</v>
+      </c>
+      <c r="J149" s="42" t="n">
+        <v>0.007570488132948805</v>
+      </c>
+      <c r="K149" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="43" t="n">
+        <v>144</v>
+      </c>
+      <c r="B150" s="44" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C150" s="43" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="D150" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E150" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F150" s="45" t="n">
+        <v>46730.975806379</v>
+      </c>
+      <c r="G150" s="45" t="n">
+        <v>55124.5392564395</v>
+      </c>
+      <c r="H150" s="45" t="n">
+        <v>8393.563450060501</v>
+      </c>
+      <c r="I150" s="46" t="n">
+        <v>0.1796145555538504</v>
+      </c>
+      <c r="J150" s="46" t="n">
+        <v>0.007536793235935368</v>
+      </c>
+      <c r="K150" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="39" t="n">
+        <v>145</v>
+      </c>
+      <c r="B151" s="40" t="inlineStr">
+        <is>
+          <t>Comoros</t>
+        </is>
+      </c>
+      <c r="C151" s="39" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="D151" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E151" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F151" s="41" t="n">
+        <v>3085.59675447872</v>
+      </c>
+      <c r="G151" s="41" t="n">
+        <v>3621.76626304343</v>
+      </c>
+      <c r="H151" s="41" t="n">
+        <v>536.1695085647102</v>
+      </c>
+      <c r="I151" s="42" t="n">
+        <v>0.1737652555495024</v>
+      </c>
+      <c r="J151" s="42" t="n">
+        <v>0.00730916196016107</v>
+      </c>
+      <c r="K151" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="43" t="n">
+        <v>146</v>
+      </c>
+      <c r="B152" s="44" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C152" s="43" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="D152" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E152" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F152" s="45" t="n">
+        <v>42223.130174522</v>
+      </c>
+      <c r="G152" s="45" t="n">
+        <v>49318.105559037</v>
+      </c>
+      <c r="H152" s="45" t="n">
+        <v>7094.975384515004</v>
+      </c>
+      <c r="I152" s="46" t="n">
+        <v>0.1680352772328615</v>
+      </c>
+      <c r="J152" s="46" t="n">
+        <v>0.007085121868066757</v>
+      </c>
+      <c r="K152" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="39" t="n">
+        <v>147</v>
+      </c>
+      <c r="B153" s="40" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C153" s="39" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="D153" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E153" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F153" s="41" t="n">
+        <v>7516.81391491319</v>
+      </c>
+      <c r="G153" s="41" t="n">
+        <v>8760.190819631511</v>
+      </c>
+      <c r="H153" s="41" t="n">
+        <v>1243.37690471832</v>
+      </c>
+      <c r="I153" s="42" t="n">
+        <v>0.1654127558288345</v>
+      </c>
+      <c r="J153" s="42" t="n">
+        <v>0.006982232049900228</v>
+      </c>
+      <c r="K153" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="n">
+        <v>148</v>
+      </c>
+      <c r="B154" s="44" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C154" s="43" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="D154" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E154" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F154" s="45" t="n">
+        <v>54919.7101911513</v>
+      </c>
+      <c r="G154" s="45" t="n">
+        <v>63970.4008534859</v>
+      </c>
+      <c r="H154" s="45" t="n">
+        <v>9050.6906623346</v>
+      </c>
+      <c r="I154" s="46" t="n">
+        <v>0.1647985874439822</v>
+      </c>
+      <c r="J154" s="46" t="n">
+        <v>0.006958104341567406</v>
+      </c>
+      <c r="K154" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="39" t="n">
+        <v>149</v>
+      </c>
+      <c r="B155" s="40" t="inlineStr">
+        <is>
+          <t>Solomon Islands</t>
+        </is>
+      </c>
+      <c r="C155" s="39" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D155" s="40" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E155" s="40" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F155" s="41" t="n">
+        <v>2050.57140389822</v>
+      </c>
+      <c r="G155" s="41" t="n">
+        <v>2382.1314520674</v>
+      </c>
+      <c r="H155" s="41" t="n">
+        <v>331.5600481691799</v>
+      </c>
+      <c r="I155" s="42" t="n">
+        <v>0.1616915399965448</v>
+      </c>
+      <c r="J155" s="42" t="n">
+        <v>0.006835857039703797</v>
+      </c>
+      <c r="K155" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="B156" s="44" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C156" s="43" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="D156" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E156" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F156" s="45" t="n">
+        <v>46505.2798806788</v>
+      </c>
+      <c r="G156" s="45" t="n">
+        <v>53993.1172607885</v>
+      </c>
+      <c r="H156" s="45" t="n">
+        <v>7487.837380109704</v>
+      </c>
+      <c r="I156" s="46" t="n">
+        <v>0.161010478795562</v>
+      </c>
+      <c r="J156" s="46" t="n">
+        <v>0.006809018872429906</v>
+      </c>
+      <c r="K156" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="39" t="n">
+        <v>151</v>
+      </c>
+      <c r="B157" s="40" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C157" s="39" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="D157" s="40" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E157" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F157" s="41" t="n">
+        <v>50139.7664579994</v>
+      </c>
+      <c r="G157" s="41" t="n">
+        <v>57989.5784653558</v>
+      </c>
+      <c r="H157" s="41" t="n">
+        <v>7849.812007356399</v>
+      </c>
+      <c r="I157" s="42" t="n">
+        <v>0.1565586073068759</v>
+      </c>
+      <c r="J157" s="42" t="n">
+        <v>0.006633215599356257</v>
+      </c>
+      <c r="K157" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="43" t="n">
+        <v>152</v>
+      </c>
+      <c r="B158" s="44" t="inlineStr">
+        <is>
+          <t>Vanuatu</t>
+        </is>
+      </c>
+      <c r="C158" s="43" t="inlineStr">
+        <is>
+          <t>VUT</t>
+        </is>
+      </c>
+      <c r="D158" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E158" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F158" s="45" t="n">
+        <v>3372.77297249271</v>
+      </c>
+      <c r="G158" s="45" t="n">
+        <v>3866.99814901674</v>
+      </c>
+      <c r="H158" s="45" t="n">
+        <v>494.2251765240303</v>
+      </c>
+      <c r="I158" s="46" t="n">
+        <v>0.1465337811215808</v>
+      </c>
+      <c r="J158" s="46" t="n">
+        <v>0.006234960925415756</v>
+      </c>
+      <c r="K158" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="39" t="n">
+        <v>153</v>
+      </c>
+      <c r="B159" s="40" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
+      <c r="C159" s="39" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="D159" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E159" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F159" s="41" t="n">
+        <v>2611.8368552722</v>
+      </c>
+      <c r="G159" s="41" t="n">
+        <v>2993.25166359257</v>
+      </c>
+      <c r="H159" s="41" t="n">
+        <v>381.41480832037</v>
+      </c>
+      <c r="I159" s="42" t="n">
+        <v>0.146033167251796</v>
+      </c>
+      <c r="J159" s="42" t="n">
+        <v>0.006214986087476282</v>
+      </c>
+      <c r="K159" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="43" t="n">
+        <v>154</v>
+      </c>
+      <c r="B160" s="44" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C160" s="43" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="D160" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E160" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F160" s="45" t="n">
+        <v>11923.1211013633</v>
+      </c>
+      <c r="G160" s="45" t="n">
+        <v>13592.0484020929</v>
+      </c>
+      <c r="H160" s="45" t="n">
+        <v>1668.9273007296</v>
+      </c>
+      <c r="I160" s="46" t="n">
+        <v>0.1399740291607685</v>
+      </c>
+      <c r="J160" s="46" t="n">
+        <v>0.005972559611783002</v>
+      </c>
+      <c r="K160" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="39" t="n">
+        <v>155</v>
+      </c>
+      <c r="B161" s="40" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C161" s="39" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="D161" s="40" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E161" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F161" s="41" t="n">
+        <v>9556.481637120531</v>
+      </c>
+      <c r="G161" s="41" t="n">
+        <v>10794.2402687732</v>
+      </c>
+      <c r="H161" s="41" t="n">
+        <v>1237.758631652669</v>
+      </c>
+      <c r="I161" s="42" t="n">
+        <v>0.1295203275277383</v>
+      </c>
+      <c r="J161" s="42" t="n">
+        <v>0.005551400125292538</v>
+      </c>
+      <c r="K161" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="n">
+        <v>156</v>
+      </c>
+      <c r="B162" s="44" t="inlineStr">
+        <is>
+          <t>West Bank and Gaza</t>
+        </is>
+      </c>
+      <c r="C162" s="43" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="D162" s="44" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E162" s="44" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F162" s="45" t="n">
+        <v>3788.92652721128</v>
+      </c>
+      <c r="G162" s="45" t="n">
+        <v>4272.45762077019</v>
+      </c>
+      <c r="H162" s="45" t="n">
+        <v>483.5310935589105</v>
+      </c>
+      <c r="I162" s="46" t="n">
+        <v>0.1276169094560928</v>
+      </c>
+      <c r="J162" s="46" t="n">
+        <v>0.005474314878239905</v>
+      </c>
+      <c r="K162" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="39" t="n">
+        <v>157</v>
+      </c>
+      <c r="B163" s="40" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C163" s="39" t="inlineStr">
+        <is>
+          <t>QAT</t>
+        </is>
+      </c>
+      <c r="D163" s="40" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E163" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F163" s="41" t="n">
+        <v>98068.1232492499</v>
+      </c>
+      <c r="G163" s="41" t="n">
+        <v>110135.696297692</v>
+      </c>
+      <c r="H163" s="41" t="n">
+        <v>12067.57304844211</v>
+      </c>
+      <c r="I163" s="42" t="n">
+        <v>0.1230529620493621</v>
+      </c>
+      <c r="J163" s="42" t="n">
+        <v>0.005288975502905968</v>
+      </c>
+      <c r="K163" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="43" t="n">
+        <v>158</v>
+      </c>
+      <c r="B164" s="44" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C164" s="43" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="D164" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E164" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F164" s="45" t="n">
+        <v>49655.5451564067</v>
+      </c>
+      <c r="G164" s="45" t="n">
+        <v>55735.2174921326</v>
+      </c>
+      <c r="H164" s="45" t="n">
+        <v>6079.672335725903</v>
+      </c>
+      <c r="I164" s="46" t="n">
+        <v>0.1224369265622993</v>
+      </c>
+      <c r="J164" s="46" t="n">
+        <v>0.005263903590790653</v>
+      </c>
+      <c r="K164" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="39" t="n">
+        <v>159</v>
+      </c>
+      <c r="B165" s="40" t="inlineStr">
+        <is>
+          <t>Puerto Rico (US)</t>
+        </is>
+      </c>
+      <c r="C165" s="39" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="D165" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E165" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F165" s="41" t="n">
+        <v>39876.0670237773</v>
+      </c>
+      <c r="G165" s="41" t="n">
+        <v>44603.218055883</v>
+      </c>
+      <c r="H165" s="41" t="n">
+        <v>4727.151032105699</v>
+      </c>
+      <c r="I165" s="42" t="n">
+        <v>0.1185460699844594</v>
+      </c>
+      <c r="J165" s="42" t="n">
+        <v>0.005105246229548221</v>
+      </c>
+      <c r="K165" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="43" t="n">
+        <v>160</v>
+      </c>
+      <c r="B166" s="44" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="C166" s="43" t="inlineStr">
+        <is>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="D166" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E166" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F166" s="45" t="n">
+        <v>10169.7500243245</v>
+      </c>
+      <c r="G166" s="45" t="n">
+        <v>11357.915592063</v>
+      </c>
+      <c r="H166" s="45" t="n">
+        <v>1188.165567738501</v>
+      </c>
+      <c r="I166" s="46" t="n">
+        <v>0.1168333110348425</v>
+      </c>
+      <c r="J166" s="46" t="n">
+        <v>0.005035238044441614</v>
+      </c>
+      <c r="K166" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="39" t="n">
+        <v>161</v>
+      </c>
+      <c r="B167" s="40" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="C167" s="39" t="inlineStr">
+        <is>
+          <t>BHR</t>
+        </is>
+      </c>
+      <c r="D167" s="40" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E167" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F167" s="41" t="n">
+        <v>54431.8763559658</v>
+      </c>
+      <c r="G167" s="41" t="n">
+        <v>60669.6307795772</v>
+      </c>
+      <c r="H167" s="41" t="n">
+        <v>6237.754423611404</v>
+      </c>
+      <c r="I167" s="42" t="n">
+        <v>0.1145974535733185</v>
+      </c>
+      <c r="J167" s="42" t="n">
+        <v>0.004943694090485673</v>
+      </c>
+      <c r="K167" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="43" t="n">
+        <v>162</v>
+      </c>
+      <c r="B168" s="44" t="inlineStr">
+        <is>
+          <t>Suriname</t>
+        </is>
+      </c>
+      <c r="C168" s="43" t="inlineStr">
+        <is>
+          <t>SUR</t>
+        </is>
+      </c>
+      <c r="D168" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E168" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F168" s="45" t="n">
+        <v>17383.5015505612</v>
+      </c>
+      <c r="G168" s="45" t="n">
+        <v>19357.3907969318</v>
+      </c>
+      <c r="H168" s="45" t="n">
+        <v>1973.8892463706</v>
+      </c>
+      <c r="I168" s="46" t="n">
+        <v>0.11354957691518</v>
+      </c>
+      <c r="J168" s="46" t="n">
+        <v>0.004900729951458738</v>
+      </c>
+      <c r="K168" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="39" t="n">
+        <v>163</v>
+      </c>
+      <c r="B169" s="40" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C169" s="39" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="D169" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E169" s="40" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F169" s="41" t="n">
+        <v>19701.4633898714</v>
+      </c>
+      <c r="G169" s="41" t="n">
+        <v>21911.9292842747</v>
+      </c>
+      <c r="H169" s="41" t="n">
+        <v>2210.465894403304</v>
+      </c>
+      <c r="I169" s="42" t="n">
+        <v>0.1121980560865197</v>
+      </c>
+      <c r="J169" s="42" t="n">
+        <v>0.004845259031826421</v>
+      </c>
+      <c r="K169" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="43" t="n">
+        <v>164</v>
+      </c>
+      <c r="B170" s="44" t="inlineStr">
+        <is>
+          <t>Burundi</t>
+        </is>
+      </c>
+      <c r="C170" s="43" t="inlineStr">
+        <is>
+          <t>BDI</t>
+        </is>
+      </c>
+      <c r="D170" s="44" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E170" s="44" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F170" s="45" t="n">
+        <v>996.569433908385</v>
+      </c>
+      <c r="G170" s="45" t="n">
+        <v>1066.51299240586</v>
+      </c>
+      <c r="H170" s="45" t="n">
+        <v>69.9435584974749</v>
+      </c>
+      <c r="I170" s="46" t="n">
+        <v>0.0701843304817884</v>
+      </c>
+      <c r="J170" s="46" t="n">
+        <v>0.003087980980443161</v>
+      </c>
+      <c r="K170" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="39" t="n">
+        <v>165</v>
+      </c>
+      <c r="B171" s="40" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="C171" s="39" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="D171" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E171" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F171" s="41" t="n">
+        <v>63656.1958332184</v>
+      </c>
+      <c r="G171" s="41" t="n">
+        <v>67993.0524178882</v>
+      </c>
+      <c r="H171" s="41" t="n">
+        <v>4336.856584669804</v>
+      </c>
+      <c r="I171" s="42" t="n">
+        <v>0.06812937103612859</v>
+      </c>
+      <c r="J171" s="42" t="n">
+        <v>0.003000349662970025</v>
+      </c>
+      <c r="K171" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="43" t="n">
+        <v>166</v>
+      </c>
+      <c r="B172" s="44" t="inlineStr">
+        <is>
+          <t>Micronesia, Fed. Sts.</t>
+        </is>
+      </c>
+      <c r="C172" s="43" t="inlineStr">
+        <is>
+          <t>FSM</t>
+        </is>
+      </c>
+      <c r="D172" s="44" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E172" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F172" s="45" t="n">
+        <v>3701.13265140057</v>
+      </c>
+      <c r="G172" s="45" t="n">
+        <v>3934.6426835411</v>
+      </c>
+      <c r="H172" s="45" t="n">
+        <v>233.5100321405298</v>
+      </c>
+      <c r="I172" s="46" t="n">
+        <v>0.06309150579949252</v>
+      </c>
+      <c r="J172" s="46" t="n">
+        <v>0.002784833111430629</v>
+      </c>
+      <c r="K172" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="39" t="n">
+        <v>167</v>
+      </c>
+      <c r="B173" s="40" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C173" s="39" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="D173" s="40" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E173" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F173" s="41" t="n">
+        <v>35970.7016808475</v>
+      </c>
+      <c r="G173" s="41" t="n">
+        <v>38218.721628616</v>
+      </c>
+      <c r="H173" s="41" t="n">
+        <v>2248.019947768495</v>
+      </c>
+      <c r="I173" s="42" t="n">
+        <v>0.0624958603174941</v>
+      </c>
+      <c r="J173" s="42" t="n">
+        <v>0.002759287374059394</v>
+      </c>
+      <c r="K173" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="43" t="n">
+        <v>168</v>
+      </c>
+      <c r="B174" s="44" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C174" s="43" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="D174" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E174" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F174" s="45" t="n">
+        <v>120403.002017933</v>
+      </c>
+      <c r="G174" s="45" t="n">
+        <v>127420.601625165</v>
+      </c>
+      <c r="H174" s="45" t="n">
+        <v>7017.599607231998</v>
+      </c>
+      <c r="I174" s="46" t="n">
+        <v>0.05828425778110402</v>
+      </c>
+      <c r="J174" s="46" t="n">
+        <v>0.002578271312265956</v>
+      </c>
+      <c r="K174" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="39" t="n">
+        <v>169</v>
+      </c>
+      <c r="B175" s="40" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="C175" s="39" t="inlineStr">
+        <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="D175" s="40" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E175" s="40" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F175" s="41" t="n">
+        <v>1584.74925232364</v>
+      </c>
+      <c r="G175" s="41" t="n">
+        <v>1668.47702330854</v>
+      </c>
+      <c r="H175" s="41" t="n">
+        <v>83.72777098490019</v>
+      </c>
+      <c r="I175" s="42" t="n">
+        <v>0.05283345037843312</v>
+      </c>
+      <c r="J175" s="42" t="n">
+        <v>0.002342970195847505</v>
+      </c>
+      <c r="K175" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="43" t="n">
+        <v>170</v>
+      </c>
+      <c r="B176" s="44" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C176" s="43" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="D176" s="44" t="inlineStr">
+        <is>
+          <t>Europe &amp; Central Asia</t>
+        </is>
+      </c>
+      <c r="E176" s="44" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F176" s="45" t="n">
+        <v>51126.2585544038</v>
+      </c>
+      <c r="G176" s="45" t="n">
+        <v>53606.0789571011</v>
+      </c>
+      <c r="H176" s="45" t="n">
+        <v>2479.820402697296</v>
+      </c>
+      <c r="I176" s="46" t="n">
+        <v>0.04850385052249617</v>
+      </c>
+      <c r="J176" s="46" t="n">
+        <v>0.002155239367757522</v>
+      </c>
+      <c r="K176" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="39" t="n">
+        <v>171</v>
+      </c>
+      <c r="B177" s="40" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
+      <c r="C177" s="39" t="inlineStr">
+        <is>
+          <t>BRB</t>
+        </is>
+      </c>
+      <c r="D177" s="40" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E177" s="40" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F177" s="41" t="n">
+        <v>21132.3281963019</v>
+      </c>
+      <c r="G177" s="41" t="n">
+        <v>22127.3604979718</v>
+      </c>
+      <c r="H177" s="41" t="n">
+        <v>995.0323016699003</v>
+      </c>
+      <c r="I177" s="42" t="n">
+        <v>0.04708578687718989</v>
+      </c>
+      <c r="J177" s="42" t="n">
+        <v>0.002093591436803655</v>
+      </c>
+      <c r="K177" s="39" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="43" t="n">
+        <v>172</v>
+      </c>
+      <c r="B178" s="44" t="inlineStr">
+        <is>
+          <t>Belize</t>
+        </is>
+      </c>
+      <c r="C178" s="43" t="inlineStr">
+        <is>
+          <t>BLZ</t>
+        </is>
+      </c>
+      <c r="D178" s="44" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E178" s="44" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F178" s="45" t="n">
+        <v>12589.2679378206</v>
+      </c>
+      <c r="G178" s="45" t="n">
+        <v>12788.8423713826</v>
+      </c>
+      <c r="H178" s="45" t="n">
+        <v>199.5744335620002</v>
+      </c>
+      <c r="I178" s="46" t="n">
+        <v>0.01585274334835951</v>
+      </c>
+      <c r="J178" s="46" t="n">
+        <v>0.0007151829397467058</v>
+      </c>
+      <c r="K178" s="43" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="55" t="n">
+        <v>173</v>
+      </c>
+      <c r="B179" s="56" t="inlineStr">
+        <is>
+          <t>Central African Republic</t>
+        </is>
+      </c>
+      <c r="C179" s="55" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="D179" s="56" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E179" s="56" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F179" s="57" t="n">
+        <v>1191.8731520062</v>
+      </c>
+      <c r="G179" s="57" t="n">
+        <v>1122.76083348097</v>
+      </c>
+      <c r="H179" s="57" t="n">
+        <v>-69.11231852522997</v>
+      </c>
+      <c r="I179" s="58" t="n">
+        <v>-0.05798630366738089</v>
+      </c>
+      <c r="J179" s="58" t="n">
+        <v>-0.002711565450832065</v>
+      </c>
+      <c r="K179" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="55" t="n">
+        <v>174</v>
+      </c>
+      <c r="B180" s="56" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="C180" s="55" t="inlineStr">
+        <is>
+          <t>GAB</t>
+        </is>
+      </c>
+      <c r="D180" s="56" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E180" s="56" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F180" s="57" t="n">
+        <v>20875.4549325844</v>
+      </c>
+      <c r="G180" s="57" t="n">
+        <v>18986.4738767293</v>
+      </c>
+      <c r="H180" s="57" t="n">
+        <v>-1888.9810558551</v>
+      </c>
+      <c r="I180" s="58" t="n">
+        <v>-0.0904881384360442</v>
+      </c>
+      <c r="J180" s="58" t="n">
+        <v>-0.004301958101835868</v>
+      </c>
+      <c r="K180" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="55" t="n">
+        <v>175</v>
+      </c>
+      <c r="B181" s="56" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="C181" s="55" t="inlineStr">
+        <is>
+          <t>OMN</t>
+        </is>
+      </c>
+      <c r="D181" s="56" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E181" s="56" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F181" s="57" t="n">
+        <v>41247.5873733105</v>
+      </c>
+      <c r="G181" s="57" t="n">
+        <v>36142.9439797194</v>
+      </c>
+      <c r="H181" s="57" t="n">
+        <v>-5104.643393591105</v>
+      </c>
+      <c r="I181" s="58" t="n">
+        <v>-0.1237561689946038</v>
+      </c>
+      <c r="J181" s="58" t="n">
+        <v>-0.005987045823748649</v>
+      </c>
+      <c r="K181" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="55" t="n">
+        <v>176</v>
+      </c>
+      <c r="B182" s="56" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C182" s="55" t="inlineStr">
+        <is>
+          <t>HTI</t>
+        </is>
+      </c>
+      <c r="D182" s="56" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="E182" s="56" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F182" s="57" t="n">
+        <v>3197.9365263707</v>
+      </c>
+      <c r="G182" s="57" t="n">
+        <v>2677.89385325549</v>
+      </c>
+      <c r="H182" s="57" t="n">
+        <v>-520.0426731152102</v>
+      </c>
+      <c r="I182" s="58" t="n">
+        <v>-0.1626181973365808</v>
+      </c>
+      <c r="J182" s="58" t="n">
+        <v>-0.00803460121557209</v>
+      </c>
+      <c r="K182" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="55" t="n">
+        <v>177</v>
+      </c>
+      <c r="B183" s="56" t="inlineStr">
+        <is>
+          <t>Congo, Rep.</t>
+        </is>
+      </c>
+      <c r="C183" s="55" t="inlineStr">
+        <is>
+          <t>COG</t>
+        </is>
+      </c>
+      <c r="D183" s="56" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E183" s="56" t="inlineStr">
+        <is>
+          <t>Lower middle income</t>
+        </is>
+      </c>
+      <c r="F183" s="57" t="n">
+        <v>7577.45630456352</v>
+      </c>
+      <c r="G183" s="57" t="n">
+        <v>6194.08981287756</v>
+      </c>
+      <c r="H183" s="57" t="n">
+        <v>-1383.36649168596</v>
+      </c>
+      <c r="I183" s="58" t="n">
+        <v>-0.1825634403002533</v>
+      </c>
+      <c r="J183" s="58" t="n">
+        <v>-0.009120966675178921</v>
+      </c>
+      <c r="K183" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="55" t="n">
+        <v>178</v>
+      </c>
+      <c r="B184" s="56" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
+      <c r="C184" s="55" t="inlineStr">
+        <is>
+          <t>LBY</t>
+        </is>
+      </c>
+      <c r="D184" s="56" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E184" s="56" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F184" s="57" t="n">
+        <v>18422.7336032405</v>
+      </c>
+      <c r="G184" s="57" t="n">
+        <v>14118.2064418565</v>
+      </c>
+      <c r="H184" s="57" t="n">
+        <v>-4304.527161384</v>
+      </c>
+      <c r="I184" s="58" t="n">
+        <v>-0.2336530101388888</v>
+      </c>
+      <c r="J184" s="58" t="n">
+        <v>-0.01202350672299957</v>
+      </c>
+      <c r="K184" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="55" t="n">
+        <v>179</v>
+      </c>
+      <c r="B185" s="56" t="inlineStr">
+        <is>
+          <t>Brunei Darussalam</t>
+        </is>
+      </c>
+      <c r="C185" s="55" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="D185" s="56" t="inlineStr">
+        <is>
+          <t>East Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="E185" s="56" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F185" s="57" t="n">
+        <v>103226.914446986</v>
+      </c>
+      <c r="G185" s="57" t="n">
+        <v>78985.12202695099</v>
+      </c>
+      <c r="H185" s="57" t="n">
+        <v>-24241.79242003501</v>
+      </c>
+      <c r="I185" s="58" t="n">
+        <v>-0.2348398433674467</v>
+      </c>
+      <c r="J185" s="58" t="n">
+        <v>-0.01209310674628739</v>
+      </c>
+      <c r="K185" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="55" t="n">
+        <v>180</v>
+      </c>
+      <c r="B186" s="56" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="C186" s="55" t="inlineStr">
+        <is>
+          <t>KWT</t>
+        </is>
+      </c>
+      <c r="D186" s="56" t="inlineStr">
+        <is>
+          <t>Middle East, North Africa, Afghanistan &amp; Pakistan</t>
+        </is>
+      </c>
+      <c r="E186" s="56" t="inlineStr">
+        <is>
+          <t>High income</t>
+        </is>
+      </c>
+      <c r="F186" s="57" t="n">
+        <v>67984.3145062554</v>
+      </c>
+      <c r="G186" s="57" t="n">
+        <v>48253.963885132</v>
+      </c>
+      <c r="H186" s="57" t="n">
+        <v>-19730.3506211234</v>
+      </c>
+      <c r="I186" s="58" t="n">
+        <v>-0.2902191595872893</v>
+      </c>
+      <c r="J186" s="58" t="n">
+        <v>-0.01546100641405812</v>
+      </c>
+      <c r="K186" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="55" t="n">
+        <v>181</v>
+      </c>
+      <c r="B187" s="56" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea</t>
+        </is>
+      </c>
+      <c r="C187" s="55" t="inlineStr">
+        <is>
+          <t>GNQ</t>
+        </is>
+      </c>
+      <c r="D187" s="56" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E187" s="56" t="inlineStr">
+        <is>
+          <t>Upper middle income</t>
+        </is>
+      </c>
+      <c r="F187" s="57" t="n">
+        <v>21709.5751241959</v>
+      </c>
+      <c r="G187" s="57" t="n">
+        <v>13786.3932934089</v>
+      </c>
+      <c r="H187" s="57" t="n">
+        <v>-7923.181830787</v>
+      </c>
+      <c r="I187" s="58" t="n">
+        <v>-0.3649625469618888</v>
+      </c>
+      <c r="J187" s="58" t="n">
+        <v>-0.02042806579586554</v>
+      </c>
+      <c r="K187" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="55" t="n">
+        <v>182</v>
+      </c>
+      <c r="B188" s="56" t="inlineStr">
+        <is>
+          <t>Sudan</t>
+        </is>
+      </c>
+      <c r="C188" s="55" t="inlineStr">
+        <is>
+          <t>SDN</t>
+        </is>
+      </c>
+      <c r="D188" s="56" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa</t>
+        </is>
+      </c>
+      <c r="E188" s="56" t="inlineStr">
+        <is>
+          <t>Low income</t>
+        </is>
+      </c>
+      <c r="F188" s="57" t="n">
+        <v>3946.92260742188</v>
+      </c>
+      <c r="G188" s="57" t="n">
+        <v>1873.38562011719</v>
+      </c>
+      <c r="H188" s="57" t="n">
+        <v>-2073.53698730469</v>
+      </c>
+      <c r="I188" s="58" t="n">
+        <v>-0.5253553701320531</v>
+      </c>
+      <c r="J188" s="58" t="n">
+        <v>-0.03330498171484875</v>
+      </c>
+      <c r="K188" s="55" t="inlineStr">
+        <is>
+          <t>Abaixo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:K188"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A3:K3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I7:I188">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00E74C3C"/>
+        <color rgb="00F7F9F9"/>
+        <color rgb="001E8449"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;LRanking PIB per capita PPC 2021 — 2003-2025</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -38001,7 +46653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
